--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44850</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45138</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>46064</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45967</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>45905</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>46132</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>46174</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>45138</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45810</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>46260</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         <v>46064</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>46064</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>46148</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>46260</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>46174</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>46191</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45905</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45568</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45964</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>45099</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
         <v>46191</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44867</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         <v>45905</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>45887</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45099</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>45940</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44472</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>46141</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>45936</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>45085</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44789</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>46038</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45952</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>46174</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>46142</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>46191</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>44484</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>45218</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>45068</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>45980</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>46125</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>46203</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>46175</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>46150</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>46239</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46048</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45393</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>45905</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>46191</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>46064</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>46108</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>44484</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>46174</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>46191</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>46283</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>45218</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46283</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44693</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44691</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44679</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>44949</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45376</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45281</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>45138</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45645</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44820</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45922</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>46146</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45937</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44970</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45943</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>45946</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45946</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>45946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45946</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45953</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>46150</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45698</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45980</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45980</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>45980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>46157</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>46162</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45272</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45007</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>45411</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>44536</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45218</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>46112</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>46112</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46125</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46128</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>46128</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45104</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>45471</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45698</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>44564</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45782</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14100,7 +14100,7 @@
         <v>46272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>46276</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46191</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45250</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>46191</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45832</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45537</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14870,7 +14870,7 @@
         <v>45698</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45391</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45698</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44889</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44853</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44495</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44484</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>44508</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>44462</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44721</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>44722</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>44577</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44862</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>44481</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>44460</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44638</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16305,7 +16305,7 @@
         <v>44754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>44714</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>44790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>44627</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         <v>44676</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>44630</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16743,7 +16743,7 @@
         <v>44862</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>44603</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>44629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>44713</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44671</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>44706</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44468</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44577</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>44505</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>44671</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44546</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44823</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44522</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>44635</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>44484</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44694</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44505</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44490</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44629</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>44459</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>44665</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>44594</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>44487</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44497</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44819</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>44463</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>44733</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>44672</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>44825</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>44622</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44875</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44491</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19109,7 +19109,7 @@
         <v>44526</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19182,7 +19182,7 @@
         <v>44889</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44602</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44777</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>44502</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>44502</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>44481</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44491</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>44784</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>44536</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>44860</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44873</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>44536</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44608</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>44539</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20292,7 +20292,7 @@
         <v>44539</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>44650</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44479</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20511,7 +20511,7 @@
         <v>44618</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20584,7 +20584,7 @@
         <v>44636</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         <v>44511</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>44490</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>44698</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>44784</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         <v>45310</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45736</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45518</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>44967</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45439</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>45107</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>44974</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45112</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45030</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>44683</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>45611</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45604</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21908,7 +21908,7 @@
         <v>45384</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>45646</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>44943</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45158</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>45751</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45054</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45530</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45183</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>44853</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45194</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45568</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22789,7 +22789,7 @@
         <v>45289</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45074</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45575</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44531</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45075</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45488</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45310</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45344</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45330</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45305</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45608</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45749</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45097</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>45610</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>45243</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45243</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45177</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>45541</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45749</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45272</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45243</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44988</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45497</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24508,7 +24508,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>44803</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45369</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>45162</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45433</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45108</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>44888</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>44928</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>44902</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>44979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45173</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45168</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44480</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45547</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45610</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45048</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>44574</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45201</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45201</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25983,7 +25983,7 @@
         <v>45518</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>44551</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>44675</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26207,7 +26207,7 @@
         <v>45441</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45441</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>44865</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26436,7 +26436,7 @@
         <v>44546</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26509,7 +26509,7 @@
         <v>45103</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45194</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26655,7 +26655,7 @@
         <v>44908</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>45471</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26801,7 +26801,7 @@
         <v>45471</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45148</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45152</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44900</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>44553</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44577</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44951</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45099</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>44503</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45131</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>45078</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45218</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45266</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27838,7 +27838,7 @@
         <v>45227</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>45188</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>45170</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45257</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         <v>45091</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28208,7 +28208,7 @@
         <v>45265</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45201</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45538</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45119</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45316</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45348</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45488</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45393</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45729</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45384</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28958,7 +28958,7 @@
         <v>45932</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         <v>45222</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>44949</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44895</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45139</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45538</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45832</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45323</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45614</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>44990</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45357</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>45884</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29854,7 +29854,7 @@
         <v>45887</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45769</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45072</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45477</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45889</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45889</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44577</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45077</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45952</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>44846</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>44594</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45642</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>45645</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30916,7 +30916,7 @@
         <v>45884</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45177</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45265</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45903</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45832</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45093</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>44522</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>45343</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>45684</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>45134</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31734,7 +31734,7 @@
         <v>44791</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>45915</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31880,7 +31880,7 @@
         <v>45559</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45237</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>44978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>44868</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>44990</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44946</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>45400</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45173</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44902</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>45925</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45252</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45099</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>46142</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45685</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45586</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45097</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45548</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33161,7 +33161,7 @@
         <v>45440</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33234,7 +33234,7 @@
         <v>45646</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>45341</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45937</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45565</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45813</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45937</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33687,7 +33687,7 @@
         <v>45714</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33760,7 +33760,7 @@
         <v>45940</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>45229</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45940</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45940</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45538</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45947</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34223,7 +34223,7 @@
         <v>45946</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34296,7 +34296,7 @@
         <v>44511</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34369,7 +34369,7 @@
         <v>45229</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45952</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>44602</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34593,7 +34593,7 @@
         <v>45877</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>45954</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45954</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45229</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45565</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34973,7 +34973,7 @@
         <v>45964</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>45303</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>45471</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44734</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44906</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>45047</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45568</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35489,7 +35489,7 @@
         <v>44984</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>45273</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>45968</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>45394</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45831</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45618</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45943</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>45974</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45817</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45974</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>46034</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45974</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>45974</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>45355</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45980</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45702</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45980</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45980</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45979</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>45980</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36994,7 +36994,7 @@
         <v>44979</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37067,7 +37067,7 @@
         <v>44958</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37140,7 +37140,7 @@
         <v>46157</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>45043</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37291,7 +37291,7 @@
         <v>46157</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37364,7 +37364,7 @@
         <v>46157</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45694</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>46160</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>46161</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>46161</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>46161</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>46161</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>45751</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45233</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>46161</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>46160</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>44981</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>46161</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38358,7 +38358,7 @@
         <v>45804</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38431,7 +38431,7 @@
         <v>45538</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>45005</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38582,7 +38582,7 @@
         <v>45005</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45628</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45404</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>46161</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>46161</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38967,7 +38967,7 @@
         <v>46161</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>46161</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39123,7 +39123,7 @@
         <v>46161</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44546</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39274,7 +39274,7 @@
         <v>45768</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39347,7 +39347,7 @@
         <v>45194</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>46162</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39498,7 +39498,7 @@
         <v>44721</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>44876</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         <v>45057</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39722,7 +39722,7 @@
         <v>45145</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45166</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45995</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39951,7 +39951,7 @@
         <v>46162</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45995</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40102,7 +40102,7 @@
         <v>45338</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>45726</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40248,7 +40248,7 @@
         <v>45726</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45159</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40394,7 +40394,7 @@
         <v>46167</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45103</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>46002</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45061</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>46167</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>46002</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>46002</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40988,7 +40988,7 @@
         <v>45523</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41061,7 +41061,7 @@
         <v>44833</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>46167</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>45982</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         <v>45982</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>44927</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45274</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41504,7 +41504,7 @@
         <v>46009</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41577,7 +41577,7 @@
         <v>46139</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>45149</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41728,7 +41728,7 @@
         <v>45523</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45766</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>46013</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45600</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45036</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45478</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45518</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45518</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42322,7 +42322,7 @@
         <v>45518</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42395,7 +42395,7 @@
         <v>45548</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45554</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>46170</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>46170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42702,7 +42702,7 @@
         <v>46170</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45125</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>45113</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>44841</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>46030</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45061</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45170</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>46035</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45562</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>46171</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45474</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45511</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>44978</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43661,7 +43661,7 @@
         <v>44963</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43734,7 +43734,7 @@
         <v>46037</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>46038</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>46174</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>46038</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45005</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>45034</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>46044</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>45582</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>46175</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>46175</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45635</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>46049</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>44740</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45194</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44776,7 +44776,7 @@
         <v>46057</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44849,7 +44849,7 @@
         <v>46056</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45628</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>46058</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45756</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>45702</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>45218</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>46071</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45590</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>46184</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>45072</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>46189</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>46189</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>46189</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45537</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>45519</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>45412</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>45387</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45387</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45141</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45400</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>44970</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>45194</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>44866</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45538</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -46621,7 +46621,7 @@
         <v>45575</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>46190</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -46772,7 +46772,7 @@
         <v>45575</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>46191</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46191</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>46191</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47084,7 +47084,7 @@
         <v>45952</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>46191</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>46191</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>46191</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46191</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46191</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>46191</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>46098</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>44621</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46101</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45009</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44566</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46198</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>46198</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>46108</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>46108</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>46108</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>45667</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45667</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -48521,7 +48521,7 @@
         <v>45575</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>44602</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45103</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>45511</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46114</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>44735</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>46113</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46114</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45111</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>46115</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>46115</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>46115</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>46115</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>46115</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>46115</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>46115</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46115</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>44883</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>45254</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45525</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46121</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>45177</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45251</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>46126</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46245</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>46125</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>46128</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>45393</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>45762</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>46245</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>46128</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45107</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>44902</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>46128</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45519</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45107</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>46203</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>44822</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>45274</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51428,7 +51428,7 @@
         <v>46133</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>46203</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45254</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45736</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>45095</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>45571</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -51881,7 +51881,7 @@
         <v>46203</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>44916</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45791</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45170</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45546</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>45211</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>44544</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>46247</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>46248</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>44473</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>45471</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -52709,7 +52709,7 @@
         <v>46206</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -52787,7 +52787,7 @@
         <v>45189</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -52860,7 +52860,7 @@
         <v>45372</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -52933,7 +52933,7 @@
         <v>46206</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>46248</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45079</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45079</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>45462</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>46206</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45575</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>46252</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>46253</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45441</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45553</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>45729</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>46254</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -53917,7 +53917,7 @@
         <v>45008</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>46254</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45113</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>45095</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45377</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>46213</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>46213</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45664</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>45274</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45280</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>46213</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>46213</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -54818,7 +54818,7 @@
         <v>46258</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>46258</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -54974,7 +54974,7 @@
         <v>46213</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55047,7 +55047,7 @@
         <v>46213</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>46213</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>46260</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>44890</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45334</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>45516</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>44753</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -55573,7 +55573,7 @@
         <v>46260</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>45251</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -55719,7 +55719,7 @@
         <v>46260</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -55797,7 +55797,7 @@
         <v>46260</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45643</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>46220</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56026,7 +56026,7 @@
         <v>46220</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>46219</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56182,7 +56182,7 @@
         <v>45569</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46265</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56333,7 +56333,7 @@
         <v>46265</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56411,7 +56411,7 @@
         <v>46220</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>46220</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -56567,7 +56567,7 @@
         <v>46265</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>46219</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45618</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -56796,7 +56796,7 @@
         <v>45119</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -56874,7 +56874,7 @@
         <v>46219</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -56947,7 +56947,7 @@
         <v>46038</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>44946</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46265</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46220</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>46038</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>46219</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46219</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>46219</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>44809</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45264</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45702</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>45219</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>44665</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>45211</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>45453</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>45777</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58150,7 +58150,7 @@
         <v>45777</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>46268</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58301,7 +58301,7 @@
         <v>45776</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>45783</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>45567</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -58520,7 +58520,7 @@
         <v>45509</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -58593,7 +58593,7 @@
         <v>46230</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -58666,7 +58666,7 @@
         <v>46272</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>45460</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>46272</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>46191</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45569</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>45253</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45203</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45229</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45267</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>46276</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>46276</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>46276</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45537</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -59655,7 +59655,7 @@
         <v>45537</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -59733,7 +59733,7 @@
         <v>46279</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -59806,7 +59806,7 @@
         <v>46191</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -59884,7 +59884,7 @@
         <v>46191</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -59962,7 +59962,7 @@
         <v>45639</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60035,7 +60035,7 @@
         <v>45181</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60113,7 +60113,7 @@
         <v>45418</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>45618</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45082</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60337,7 +60337,7 @@
         <v>45667</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>45546</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>45440</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>45793</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -60639,7 +60639,7 @@
         <v>45456</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45795</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -60790,7 +60790,7 @@
         <v>45155</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -60863,7 +60863,7 @@
         <v>45244</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -60936,7 +60936,7 @@
         <v>45796</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61014,7 +61014,7 @@
         <v>46283</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45796</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>45796</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61243,7 +61243,7 @@
         <v>45456</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61316,7 +61316,7 @@
         <v>45590</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>45812</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61467,7 +61467,7 @@
         <v>45821</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>45827</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45523</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>45832</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>45832</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -61852,7 +61852,7 @@
         <v>45832</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45832</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>45835</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45516</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>45845</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45520</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45845</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>44728</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>45694</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>45670</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45534</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>45831</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>45575</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -62831,7 +62831,7 @@
         <v>45874</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45876</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45880</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63055,7 +63055,7 @@
         <v>44172</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>44172</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>44246</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63289,7 +63289,7 @@
         <v>45578</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63362,7 +63362,7 @@
         <v>45218</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63440,7 +63440,7 @@
         <v>45040</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63513,7 +63513,7 @@
         <v>45716</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>45777</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -63669,7 +63669,7 @@
         <v>45714</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -63742,7 +63742,7 @@
         <v>45832</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45980</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -63898,7 +63898,7 @@
         <v>46094</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>46111</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64049,7 +64049,7 @@
         <v>46128</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>46245</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44850</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>45905</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>46064</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46064</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>45967</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45138</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45905</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>46285</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>46132</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 24977-2026</t>
+          <t>A 35174-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46174</v>
+        <v>46260</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,14 +3290,19 @@
           <t>LINDESBERG</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>11.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>2</v>
@@ -3324,12 +3329,129 @@
         <v>9</v>
       </c>
       <c r="T23" t="n">
+        <v>30</v>
+      </c>
+      <c r="U23" t="n">
+        <v>30</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Tretåig hackspett
+Vedtrappmossa
+Fönsterlav
+Grå renlav
+Gulvit renlav
+Skogsstjärna
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/artfynd/A 35174-2026 artfynd.xlsx", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor/A 35174-2026 karta.png", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor_geotiff/A 35174-2026 georefererad karta.tif", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomål/A 35174-2026 FSC-klagomål.docx", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomålsmail/A 35174-2026 FSC-klagomål mail.docx", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsyn/A 35174-2026 tillsynsbegäran.docx", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsynsmail/A 35174-2026 tillsynsbegäran mail.docx", "A 35174-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1885/fåglar/A 35174-2026 prioriterade fågelarter.docx", "A 35174-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 24977-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LINDESBERG</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="n">
         <v>19</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>19</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart skogssnigel
@@ -3342,120 +3464,120 @@
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/artfynd/A 24977-2026 artfynd.xlsx", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor/A 24977-2026 karta.png", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor_geotiff/A 24977-2026 georefererad karta.tif", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/knärot/A 24977-2026 karta knärot.png", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomål/A 24977-2026 FSC-klagomål.docx", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomålsmail/A 24977-2026 FSC-klagomål mail.docx", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsyn/A 24977-2026 tillsynsbegäran.docx", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsynsmail/A 24977-2026 tillsynsbegäran mail.docx", "A 24977-2026")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/fåglar/A 24977-2026 prioriterade fågelarter.docx", "A 24977-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 29409-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>LINDESBERG</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="E25" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LINDESBERG</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I25" t="n">
         <v>7.9</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>5</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S25" t="n">
         <v>9</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>20</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>20</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Duvhök
@@ -3468,111 +3590,111 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/artfynd/A 29409-2026 artfynd.xlsx", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor/A 29409-2026 karta.png", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor_geotiff/A 29409-2026 georefererad karta.tif", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomål/A 29409-2026 FSC-klagomål.docx", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomålsmail/A 29409-2026 FSC-klagomål mail.docx", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsyn/A 29409-2026 tillsynsbegäran.docx", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsynsmail/A 29409-2026 tillsynsbegäran mail.docx", "A 29409-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/fåglar/A 29409-2026 prioriterade fågelarter.docx", "A 29409-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 26749-2025</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45810</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>LINDESBERG</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LINDESBERG</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>4</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>8</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>8</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>14</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>7</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Gulsparv
@@ -3584,161 +3706,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/artfynd/A 26749-2025 artfynd.xlsx", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor/A 26749-2025 karta.png", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor_geotiff/A 26749-2025 georefererad karta.tif", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="Z25">
+      <c r="Z26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/knärot/A 26749-2025 karta knärot.png", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomål/A 26749-2025 FSC-klagomål.docx", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomålsmail/A 26749-2025 FSC-klagomål mail.docx", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsyn/A 26749-2025 tillsynsbegäran.docx", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsynsmail/A 26749-2025 tillsynsbegäran mail.docx", "A 26749-2025")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1885/fåglar/A 26749-2025 prioriterade fågelarter.docx", "A 26749-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 35174-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46292</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>LINDESBERG</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>8</v>
-      </c>
-      <c r="T26" t="n">
-        <v>29</v>
-      </c>
-      <c r="U26" t="n">
-        <v>29</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Vedtrappmossa
-Fönsterlav
-Grå renlav
-Gulvit renlav
-Skogsstjärna
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/artfynd/A 35174-2026 artfynd.xlsx", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor/A 35174-2026 karta.png", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/kartor_geotiff/A 35174-2026 georefererad karta.tif", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomål/A 35174-2026 FSC-klagomål.docx", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/klagomålsmail/A 35174-2026 FSC-klagomål mail.docx", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsyn/A 35174-2026 tillsynsbegäran.docx", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/tillsynsmail/A 35174-2026 tillsynsbegäran mail.docx", "A 35174-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1885/fåglar/A 35174-2026 prioriterade fågelarter.docx", "A 35174-2026")</f>
         <v/>
       </c>
     </row>
@@ -3762,7 +3763,7 @@
         <v>46064</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3878,7 +3879,7 @@
         <v>46289</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3995,7 +3996,7 @@
         <v>45138</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4120,7 +4121,7 @@
         <v>46289</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4237,7 +4238,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4352,7 +4353,7 @@
         <v>46148</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4471,7 +4472,7 @@
         <v>46260</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4591,7 +4592,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4706,7 +4707,7 @@
         <v>46191</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4826,7 +4827,7 @@
         <v>46191</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4946,7 +4947,7 @@
         <v>45905</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5061,7 +5062,7 @@
         <v>45964</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5179,7 +5180,7 @@
         <v>45568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5298,7 +5299,7 @@
         <v>45099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5413,7 +5414,7 @@
         <v>46191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5532,7 +5533,7 @@
         <v>45021</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5642,7 +5643,7 @@
         <v>44867</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5752,7 +5753,7 @@
         <v>45905</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5867,7 +5868,7 @@
         <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5986,7 +5987,7 @@
         <v>45940</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6100,7 +6101,7 @@
         <v>46289</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6214,7 +6215,7 @@
         <v>45099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6328,7 +6329,7 @@
         <v>44472</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6440,7 +6441,7 @@
         <v>44789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6552,7 +6553,7 @@
         <v>45936</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6669,7 +6670,7 @@
         <v>46038</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6777,7 +6778,7 @@
         <v>45952</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6889,7 +6890,7 @@
         <v>46141</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7001,7 +7002,7 @@
         <v>46174</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7113,7 +7114,7 @@
         <v>46142</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7230,7 +7231,7 @@
         <v>46191</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7347,7 +7348,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7460,7 +7461,7 @@
         <v>46289</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7573,7 +7574,7 @@
         <v>45085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7681,7 +7682,7 @@
         <v>44484</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7792,7 +7793,7 @@
         <v>46125</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7904,7 +7905,7 @@
         <v>45980</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8016,7 +8017,7 @@
         <v>46139</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8127,7 +8128,7 @@
         <v>46191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8239,7 +8240,7 @@
         <v>46150</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8355,7 +8356,7 @@
         <v>46175</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8471,7 +8472,7 @@
         <v>46239</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8583,7 +8584,7 @@
         <v>46203</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8699,7 +8700,7 @@
         <v>45068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8806,7 +8807,7 @@
         <v>46048</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8913,7 +8914,7 @@
         <v>45905</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9028,7 +9029,7 @@
         <v>46064</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9134,7 +9135,7 @@
         <v>46108</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9244,7 +9245,7 @@
         <v>45393</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9355,7 +9356,7 @@
         <v>46191</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9466,7 +9467,7 @@
         <v>46174</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9572,7 +9573,7 @@
         <v>46191</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9687,7 +9688,7 @@
         <v>46283</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9798,7 +9799,7 @@
         <v>46289</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9909,7 +9910,7 @@
         <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10015,7 +10016,7 @@
         <v>46289</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10126,7 +10127,7 @@
         <v>46289</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10237,7 +10238,7 @@
         <v>44484</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10343,7 +10344,7 @@
         <v>45218</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10454,7 +10455,7 @@
         <v>46283</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10565,7 +10566,7 @@
         <v>44512</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10670,7 +10671,7 @@
         <v>44693</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10780,7 +10781,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10885,7 +10886,7 @@
         <v>44679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10994,7 +10995,7 @@
         <v>45698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11104,7 +11105,7 @@
         <v>45698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11214,7 +11215,7 @@
         <v>45698</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11324,7 +11325,7 @@
         <v>45218</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11434,7 +11435,7 @@
         <v>45922</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11544,7 +11545,7 @@
         <v>45007</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11654,7 +11655,7 @@
         <v>44949</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11759,7 +11760,7 @@
         <v>45937</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11869,7 +11870,7 @@
         <v>45943</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11979,7 +11980,7 @@
         <v>45946</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12089,7 +12090,7 @@
         <v>45946</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12199,7 +12200,7 @@
         <v>45946</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12309,7 +12310,7 @@
         <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12419,7 +12420,7 @@
         <v>45953</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12529,7 +12530,7 @@
         <v>46112</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12638,7 +12639,7 @@
         <v>46112</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12747,7 +12748,7 @@
         <v>46125</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12857,7 +12858,7 @@
         <v>46128</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12967,7 +12968,7 @@
         <v>46128</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13077,7 +13078,7 @@
         <v>45980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13187,7 +13188,7 @@
         <v>45980</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13297,7 +13298,7 @@
         <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13407,7 +13408,7 @@
         <v>44820</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13512,7 +13513,7 @@
         <v>45138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13626,7 +13627,7 @@
         <v>46146</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13736,7 +13737,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13841,7 +13842,7 @@
         <v>45832</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13951,7 +13952,7 @@
         <v>46150</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14061,7 +14062,7 @@
         <v>46157</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14170,7 +14171,7 @@
         <v>46162</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14284,7 +14285,7 @@
         <v>45537</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14394,7 +14395,7 @@
         <v>45104</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14504,7 +14505,7 @@
         <v>44536</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14613,7 +14614,7 @@
         <v>46272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14723,7 +14724,7 @@
         <v>44970</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14828,7 +14829,7 @@
         <v>45272</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14933,7 +14934,7 @@
         <v>46276</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15043,7 +15044,7 @@
         <v>46191</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15153,7 +15154,7 @@
         <v>45471</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15258,7 +15259,7 @@
         <v>45250</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15368,7 +15369,7 @@
         <v>46191</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15478,7 +15479,7 @@
         <v>45281</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15583,7 +15584,7 @@
         <v>45376</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15688,7 +15689,7 @@
         <v>44522</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15793,7 +15794,7 @@
         <v>45411</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15902,7 +15903,7 @@
         <v>45645</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16012,7 +16013,7 @@
         <v>45782</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16122,7 +16123,7 @@
         <v>45698</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16232,7 +16233,7 @@
         <v>45391</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16342,7 +16343,7 @@
         <v>45698</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16452,7 +16453,7 @@
         <v>44889</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16525,7 +16526,7 @@
         <v>44853</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16598,7 +16599,7 @@
         <v>44495</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16671,7 +16672,7 @@
         <v>44484</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16744,7 +16745,7 @@
         <v>44508</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16817,7 +16818,7 @@
         <v>44503</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16890,7 +16891,7 @@
         <v>44613</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16963,7 +16964,7 @@
         <v>44721</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17036,7 +17037,7 @@
         <v>44722</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17109,7 +17110,7 @@
         <v>44577</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17182,7 +17183,7 @@
         <v>44862</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17260,7 +17261,7 @@
         <v>44481</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17333,7 +17334,7 @@
         <v>44638</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17406,7 +17407,7 @@
         <v>44754</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17479,7 +17480,7 @@
         <v>44714</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17552,7 +17553,7 @@
         <v>44790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17625,7 +17626,7 @@
         <v>44627</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17698,7 +17699,7 @@
         <v>44676</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17771,7 +17772,7 @@
         <v>44630</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17844,7 +17845,7 @@
         <v>44862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17922,7 +17923,7 @@
         <v>44603</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17995,7 +17996,7 @@
         <v>44713</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18073,7 +18074,7 @@
         <v>44671</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18146,7 +18147,7 @@
         <v>44706</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18224,7 +18225,7 @@
         <v>44468</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18302,7 +18303,7 @@
         <v>44577</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18375,7 +18376,7 @@
         <v>44671</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18448,7 +18449,7 @@
         <v>44505</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18521,7 +18522,7 @@
         <v>44546</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18594,7 +18595,7 @@
         <v>44823</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18667,7 +18668,7 @@
         <v>44522</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18740,7 +18741,7 @@
         <v>44635</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18813,7 +18814,7 @@
         <v>44484</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18886,7 +18887,7 @@
         <v>44694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18964,7 +18965,7 @@
         <v>44505</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19037,7 +19038,7 @@
         <v>44490</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19110,7 +19111,7 @@
         <v>44629</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19183,7 +19184,7 @@
         <v>44665</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19256,7 +19257,7 @@
         <v>44594</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19329,7 +19330,7 @@
         <v>44487</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19402,7 +19403,7 @@
         <v>44497</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19475,7 +19476,7 @@
         <v>44819</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19548,7 +19549,7 @@
         <v>44733</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19621,7 +19622,7 @@
         <v>44672</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19694,7 +19695,7 @@
         <v>44825</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19772,7 +19773,7 @@
         <v>44622</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19845,7 +19846,7 @@
         <v>44875</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19918,7 +19919,7 @@
         <v>44491</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19991,7 +19992,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20064,7 +20065,7 @@
         <v>44889</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20137,7 +20138,7 @@
         <v>44602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20210,7 +20211,7 @@
         <v>44777</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20283,7 +20284,7 @@
         <v>44665</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20356,7 +20357,7 @@
         <v>44502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20429,7 +20430,7 @@
         <v>44502</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20502,7 +20503,7 @@
         <v>44481</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20575,7 +20576,7 @@
         <v>44491</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20648,7 +20649,7 @@
         <v>44784</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20721,7 +20722,7 @@
         <v>44536</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20794,7 +20795,7 @@
         <v>44860</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20872,7 +20873,7 @@
         <v>44873</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20950,7 +20951,7 @@
         <v>44536</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21023,7 +21024,7 @@
         <v>44608</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21101,7 +21102,7 @@
         <v>44539</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21174,7 +21175,7 @@
         <v>44539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21247,7 +21248,7 @@
         <v>44650</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21320,7 +21321,7 @@
         <v>44479</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21393,7 +21394,7 @@
         <v>44618</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21466,7 +21467,7 @@
         <v>44636</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21539,7 +21540,7 @@
         <v>44511</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21612,7 +21613,7 @@
         <v>44490</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21685,7 +21686,7 @@
         <v>44698</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21763,7 +21764,7 @@
         <v>44784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21836,7 +21837,7 @@
         <v>45194</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21909,7 +21910,7 @@
         <v>45338</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21982,7 +21983,7 @@
         <v>45274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22055,7 +22056,7 @@
         <v>45355</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22128,7 +22129,7 @@
         <v>45412</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22201,7 +22202,7 @@
         <v>45091</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22274,7 +22275,7 @@
         <v>44890</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22347,7 +22348,7 @@
         <v>45433</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22420,7 +22421,7 @@
         <v>45222</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22493,7 +22494,7 @@
         <v>45384</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22566,7 +22567,7 @@
         <v>45471</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22639,7 +22640,7 @@
         <v>45243</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22712,7 +22713,7 @@
         <v>45243</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22790,7 +22791,7 @@
         <v>45243</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22868,7 +22869,7 @@
         <v>45061</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22941,7 +22942,7 @@
         <v>44809</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23014,7 +23015,7 @@
         <v>45518</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23092,7 +23093,7 @@
         <v>44876</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23170,7 +23171,7 @@
         <v>44866</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23243,7 +23244,7 @@
         <v>44902</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23321,7 +23322,7 @@
         <v>45796</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23399,7 +23400,7 @@
         <v>45099</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23477,7 +23478,7 @@
         <v>45323</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23550,7 +23551,7 @@
         <v>45795</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23623,7 +23624,7 @@
         <v>45796</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23701,7 +23702,7 @@
         <v>45796</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23779,7 +23780,7 @@
         <v>45112</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23852,7 +23853,7 @@
         <v>45274</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23925,7 +23926,7 @@
         <v>45152</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24003,7 +24004,7 @@
         <v>45518</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24076,7 +24077,7 @@
         <v>45134</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24149,7 +24150,7 @@
         <v>46030</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24222,7 +24223,7 @@
         <v>45244</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24295,7 +24296,7 @@
         <v>44883</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24368,7 +24369,7 @@
         <v>45456</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24441,7 +24442,7 @@
         <v>45793</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24519,7 +24520,7 @@
         <v>45884</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24592,7 +24593,7 @@
         <v>45538</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24670,7 +24671,7 @@
         <v>45590</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24743,7 +24744,7 @@
         <v>45441</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24821,7 +24822,7 @@
         <v>45441</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24899,7 +24900,7 @@
         <v>45155</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24972,7 +24973,7 @@
         <v>45456</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25050,7 +25051,7 @@
         <v>45005</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25123,7 +25124,7 @@
         <v>45005</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25201,7 +25202,7 @@
         <v>45887</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25279,7 +25280,7 @@
         <v>45488</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25352,7 +25353,7 @@
         <v>44978</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25425,7 +25426,7 @@
         <v>45586</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25498,7 +25499,7 @@
         <v>46035</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25571,7 +25572,7 @@
         <v>45889</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25649,7 +25650,7 @@
         <v>45889</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25727,7 +25728,7 @@
         <v>45441</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25800,7 +25801,7 @@
         <v>44602</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25873,7 +25874,7 @@
         <v>46037</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25946,7 +25947,7 @@
         <v>44602</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26019,7 +26020,7 @@
         <v>46038</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26092,7 +26093,7 @@
         <v>46038</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26165,7 +26166,7 @@
         <v>45538</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26238,7 +26239,7 @@
         <v>46044</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26311,7 +26312,7 @@
         <v>44988</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26389,7 +26390,7 @@
         <v>45903</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26467,7 +26468,7 @@
         <v>45393</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26545,7 +26546,7 @@
         <v>46049</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26618,7 +26619,7 @@
         <v>45726</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26691,7 +26692,7 @@
         <v>45726</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26764,7 +26765,7 @@
         <v>45571</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26842,7 +26843,7 @@
         <v>44544</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26915,7 +26916,7 @@
         <v>44841</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26988,7 +26989,7 @@
         <v>45645</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27066,7 +27067,7 @@
         <v>45280</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27144,7 +27145,7 @@
         <v>45541</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27222,7 +27223,7 @@
         <v>46056</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27295,7 +27296,7 @@
         <v>45519</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27373,7 +27374,7 @@
         <v>46058</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27446,7 +27447,7 @@
         <v>44908</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27519,7 +27520,7 @@
         <v>45518</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27592,7 +27593,7 @@
         <v>45749</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27665,7 +27666,7 @@
         <v>46057</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27738,7 +27739,7 @@
         <v>44574</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27811,7 +27812,7 @@
         <v>44553</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27884,7 +27885,7 @@
         <v>44594</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27957,7 +27958,7 @@
         <v>45400</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28035,7 +28036,7 @@
         <v>46071</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28108,7 +28109,7 @@
         <v>45925</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28186,7 +28187,7 @@
         <v>45201</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28264,7 +28265,7 @@
         <v>45565</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28337,7 +28338,7 @@
         <v>44888</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28410,7 +28411,7 @@
         <v>45562</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28483,7 +28484,7 @@
         <v>45565</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28556,7 +28557,7 @@
         <v>45553</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28634,7 +28635,7 @@
         <v>44974</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28707,7 +28708,7 @@
         <v>44949</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28780,7 +28781,7 @@
         <v>44943</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28853,7 +28854,7 @@
         <v>44979</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28926,7 +28927,7 @@
         <v>45201</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29004,7 +29005,7 @@
         <v>45201</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29082,7 +29083,7 @@
         <v>45937</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29160,7 +29161,7 @@
         <v>45229</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29238,7 +29239,7 @@
         <v>45194</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29311,7 +29312,7 @@
         <v>44740</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29384,7 +29385,7 @@
         <v>45813</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29457,7 +29458,7 @@
         <v>45937</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29535,7 +29536,7 @@
         <v>45394</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29608,7 +29609,7 @@
         <v>45582</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29686,7 +29687,7 @@
         <v>45769</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29759,7 +29760,7 @@
         <v>45940</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29837,7 +29838,7 @@
         <v>45940</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29915,7 +29916,7 @@
         <v>45940</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29993,7 +29994,7 @@
         <v>45387</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30066,7 +30067,7 @@
         <v>45387</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30139,7 +30140,7 @@
         <v>46098</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30217,7 +30218,7 @@
         <v>45946</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30290,7 +30291,7 @@
         <v>45377</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30363,7 +30364,7 @@
         <v>45548</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30441,7 +30442,7 @@
         <v>46101</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30514,7 +30515,7 @@
         <v>45569</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30587,7 +30588,7 @@
         <v>45095</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30660,7 +30661,7 @@
         <v>45095</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30733,7 +30734,7 @@
         <v>45947</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30811,7 +30812,7 @@
         <v>45251</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30884,7 +30885,7 @@
         <v>45952</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30957,7 +30958,7 @@
         <v>44963</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31030,7 +31031,7 @@
         <v>45812</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31108,7 +31109,7 @@
         <v>44735</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31186,7 +31187,7 @@
         <v>45266</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31259,7 +31260,7 @@
         <v>46108</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31332,7 +31333,7 @@
         <v>46108</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31405,7 +31406,7 @@
         <v>44967</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31478,7 +31479,7 @@
         <v>46108</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31551,7 +31552,7 @@
         <v>46113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31629,7 +31630,7 @@
         <v>44970</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31702,7 +31703,7 @@
         <v>45348</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31775,7 +31776,7 @@
         <v>46115</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31848,7 +31849,7 @@
         <v>46115</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31921,7 +31922,7 @@
         <v>46114</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31994,7 +31995,7 @@
         <v>46114</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32067,7 +32068,7 @@
         <v>46115</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32140,7 +32141,7 @@
         <v>46115</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32213,7 +32214,7 @@
         <v>46115</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32286,7 +32287,7 @@
         <v>46115</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32359,7 +32360,7 @@
         <v>46115</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32432,7 +32433,7 @@
         <v>46115</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32505,7 +32506,7 @@
         <v>45099</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32583,7 +32584,7 @@
         <v>45964</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32656,7 +32657,7 @@
         <v>46121</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32729,7 +32730,7 @@
         <v>45635</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32802,7 +32803,7 @@
         <v>46125</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32875,7 +32876,7 @@
         <v>45968</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32953,7 +32954,7 @@
         <v>45628</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33026,7 +33027,7 @@
         <v>45344</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33099,7 +33100,7 @@
         <v>45034</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33172,7 +33173,7 @@
         <v>45194</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33245,7 +33246,7 @@
         <v>45974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33323,7 +33324,7 @@
         <v>45974</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33396,7 +33397,7 @@
         <v>46126</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33469,7 +33470,7 @@
         <v>45974</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33547,7 +33548,7 @@
         <v>46128</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33625,7 +33626,7 @@
         <v>45009</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33698,7 +33699,7 @@
         <v>46128</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33776,7 +33777,7 @@
         <v>46128</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33854,7 +33855,7 @@
         <v>44503</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33927,7 +33928,7 @@
         <v>45145</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34005,7 +34006,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34083,7 +34084,7 @@
         <v>45159</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34156,7 +34157,7 @@
         <v>45980</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34234,7 +34235,7 @@
         <v>45979</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34312,7 +34313,7 @@
         <v>45980</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34390,7 +34391,7 @@
         <v>45980</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34468,7 +34469,7 @@
         <v>45488</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34541,7 +34542,7 @@
         <v>46133</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34614,7 +34615,7 @@
         <v>45538</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34692,7 +34693,7 @@
         <v>45511</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34765,7 +34766,7 @@
         <v>45511</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34838,7 +34839,7 @@
         <v>44951</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34911,7 +34912,7 @@
         <v>45832</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34989,7 +34990,7 @@
         <v>45538</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35067,7 +35068,7 @@
         <v>44665</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35140,7 +35141,7 @@
         <v>45149</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35218,7 +35219,7 @@
         <v>45646</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35291,7 +35292,7 @@
         <v>45791</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35364,7 +35365,7 @@
         <v>45995</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35437,7 +35438,7 @@
         <v>45995</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35510,7 +35511,7 @@
         <v>45170</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35588,7 +35589,7 @@
         <v>45072</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35666,7 +35667,7 @@
         <v>44546</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35739,7 +35740,7 @@
         <v>45915</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35812,7 +35813,7 @@
         <v>45113</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35885,7 +35886,7 @@
         <v>45139</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35963,7 +35964,7 @@
         <v>44990</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36036,7 +36037,7 @@
         <v>45932</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36109,7 +36110,7 @@
         <v>46002</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36182,7 +36183,7 @@
         <v>45252</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36255,7 +36256,7 @@
         <v>45530</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36328,7 +36329,7 @@
         <v>45030</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36406,7 +36407,7 @@
         <v>45952</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36484,7 +36485,7 @@
         <v>45982</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36557,7 +36558,7 @@
         <v>45642</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36630,7 +36631,7 @@
         <v>45982</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36703,7 +36704,7 @@
         <v>45614</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36776,7 +36777,7 @@
         <v>45194</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36849,7 +36850,7 @@
         <v>46009</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36922,7 +36923,7 @@
         <v>45559</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37000,7 +37001,7 @@
         <v>46013</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37073,7 +37074,7 @@
         <v>44900</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37146,7 +37147,7 @@
         <v>45821</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37224,7 +37225,7 @@
         <v>44511</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37297,7 +37298,7 @@
         <v>45832</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37375,7 +37376,7 @@
         <v>45766</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37448,7 +37449,7 @@
         <v>45211</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37521,7 +37522,7 @@
         <v>44566</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37594,7 +37595,7 @@
         <v>44990</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37667,7 +37668,7 @@
         <v>45093</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37740,7 +37741,7 @@
         <v>46142</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37818,7 +37819,7 @@
         <v>45251</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37891,7 +37892,7 @@
         <v>45736</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37964,7 +37965,7 @@
         <v>45827</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38042,7 +38043,7 @@
         <v>44791</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38115,7 +38116,7 @@
         <v>45077</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38193,7 +38194,7 @@
         <v>45106</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38266,7 +38267,7 @@
         <v>45075</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38344,7 +38345,7 @@
         <v>44946</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38417,7 +38418,7 @@
         <v>45523</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38490,7 +38491,7 @@
         <v>45832</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38568,7 +38569,7 @@
         <v>45832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38646,7 +38647,7 @@
         <v>45264</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38719,7 +38720,7 @@
         <v>45393</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38797,7 +38798,7 @@
         <v>45832</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38875,7 +38876,7 @@
         <v>45832</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38953,7 +38954,7 @@
         <v>45548</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39031,7 +39032,7 @@
         <v>44928</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39104,7 +39105,7 @@
         <v>45877</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39182,7 +39183,7 @@
         <v>44927</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39255,7 +39256,7 @@
         <v>45618</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39333,7 +39334,7 @@
         <v>45817</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39406,7 +39407,7 @@
         <v>45831</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39479,7 +39480,7 @@
         <v>45943</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39552,7 +39553,7 @@
         <v>46034</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39625,7 +39626,7 @@
         <v>45835</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39698,7 +39699,7 @@
         <v>45600</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39771,7 +39772,7 @@
         <v>46157</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39849,7 +39850,7 @@
         <v>46157</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39922,7 +39923,7 @@
         <v>46160</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39995,7 +39996,7 @@
         <v>46157</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40073,7 +40074,7 @@
         <v>46160</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40146,7 +40147,7 @@
         <v>46161</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40224,7 +40225,7 @@
         <v>45316</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40297,7 +40298,7 @@
         <v>46162</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40375,7 +40376,7 @@
         <v>46161</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40453,7 +40454,7 @@
         <v>45516</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40531,7 +40532,7 @@
         <v>45177</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40609,7 +40610,7 @@
         <v>45751</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40682,7 +40683,7 @@
         <v>45108</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40755,7 +40756,7 @@
         <v>45751</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40828,7 +40829,7 @@
         <v>45702</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40901,7 +40902,7 @@
         <v>46161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40979,7 +40980,7 @@
         <v>46161</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41057,7 +41058,7 @@
         <v>46161</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41135,7 +41136,7 @@
         <v>46161</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41213,7 +41214,7 @@
         <v>46161</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41291,7 +41292,7 @@
         <v>46161</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41369,7 +41370,7 @@
         <v>46161</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41447,7 +41448,7 @@
         <v>45804</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41520,7 +41521,7 @@
         <v>46161</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41598,7 +41599,7 @@
         <v>46161</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41676,7 +41677,7 @@
         <v>45103</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41749,7 +41750,7 @@
         <v>45119</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41827,7 +41828,7 @@
         <v>45520</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41905,7 +41906,7 @@
         <v>45845</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41978,7 +41979,7 @@
         <v>45845</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42051,7 +42052,7 @@
         <v>45107</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42124,7 +42125,7 @@
         <v>45694</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42202,7 +42203,7 @@
         <v>46139</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42275,7 +42276,7 @@
         <v>46167</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42353,7 +42354,7 @@
         <v>46167</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42431,7 +42432,7 @@
         <v>45694</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42504,7 +42505,7 @@
         <v>44728</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42577,7 +42578,7 @@
         <v>46167</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42655,7 +42656,7 @@
         <v>45670</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42728,7 +42729,7 @@
         <v>45554</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42806,7 +42807,7 @@
         <v>44531</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42879,7 +42880,7 @@
         <v>46170</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42957,7 +42958,7 @@
         <v>45575</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43035,7 +43036,7 @@
         <v>45162</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43108,7 +43109,7 @@
         <v>46171</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43181,7 +43182,7 @@
         <v>45279</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43254,7 +43255,7 @@
         <v>45519</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43332,7 +43333,7 @@
         <v>45537</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43405,7 +43406,7 @@
         <v>46170</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43478,7 +43479,7 @@
         <v>46170</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43551,7 +43552,7 @@
         <v>46175</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43629,7 +43630,7 @@
         <v>45107</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43707,7 +43708,7 @@
         <v>46175</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43785,7 +43786,7 @@
         <v>46174</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43863,7 +43864,7 @@
         <v>45575</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43941,7 +43942,7 @@
         <v>45005</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44014,7 +44015,7 @@
         <v>45608</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44092,7 +44093,7 @@
         <v>45831</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44165,7 +44166,7 @@
         <v>45546</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44243,7 +44244,7 @@
         <v>45534</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44321,7 +44322,7 @@
         <v>44551</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44394,7 +44395,7 @@
         <v>44480</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44467,7 +44468,7 @@
         <v>45289</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44540,7 +44541,7 @@
         <v>44981</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44613,7 +44614,7 @@
         <v>45148</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44686,7 +44687,7 @@
         <v>45141</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44759,7 +44760,7 @@
         <v>45113</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44832,7 +44833,7 @@
         <v>45518</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44905,7 +44906,7 @@
         <v>45518</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44978,7 +44979,7 @@
         <v>45643</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45051,7 +45052,7 @@
         <v>46184</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45124,7 +45125,7 @@
         <v>45140</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45197,7 +45198,7 @@
         <v>45646</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45270,7 +45271,7 @@
         <v>46189</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45343,7 +45344,7 @@
         <v>45874</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45421,7 +45422,7 @@
         <v>46189</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45494,7 +45495,7 @@
         <v>46189</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45567,7 +45568,7 @@
         <v>45575</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45645,7 +45646,7 @@
         <v>45170</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45723,7 +45724,7 @@
         <v>45343</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45796,7 +45797,7 @@
         <v>46191</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45874,7 +45875,7 @@
         <v>46191</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45952,7 +45953,7 @@
         <v>46191</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46030,7 +46031,7 @@
         <v>46191</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46108,7 +46109,7 @@
         <v>46190</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46181,7 +46182,7 @@
         <v>46191</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46259,7 +46260,7 @@
         <v>45575</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46337,7 +46338,7 @@
         <v>46191</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46415,7 +46416,7 @@
         <v>46191</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46493,7 +46494,7 @@
         <v>46191</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46571,7 +46572,7 @@
         <v>45219</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46649,7 +46650,7 @@
         <v>45952</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46727,7 +46728,7 @@
         <v>45876</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -46800,7 +46801,7 @@
         <v>45330</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -46873,7 +46874,7 @@
         <v>45177</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -46951,7 +46952,7 @@
         <v>44522</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47024,7 +47025,7 @@
         <v>44621</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47097,7 +47098,7 @@
         <v>45880</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47170,7 +47171,7 @@
         <v>45054</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47243,7 +47244,7 @@
         <v>45218</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47321,7 +47322,7 @@
         <v>46198</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47399,7 +47400,7 @@
         <v>46198</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47472,7 +47473,7 @@
         <v>46203</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47550,7 +47551,7 @@
         <v>46203</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47628,7 +47629,7 @@
         <v>46203</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47706,7 +47707,7 @@
         <v>45884</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47779,7 +47780,7 @@
         <v>45131</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -47852,7 +47853,7 @@
         <v>45310</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -47925,7 +47926,7 @@
         <v>44683</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -47998,7 +47999,7 @@
         <v>45667</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48071,7 +48072,7 @@
         <v>45610</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48144,7 +48145,7 @@
         <v>45173</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48217,7 +48218,7 @@
         <v>46206</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48295,7 +48296,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48373,7 +48374,7 @@
         <v>45168</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48446,7 +48447,7 @@
         <v>45372</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48519,7 +48520,7 @@
         <v>45645</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48597,7 +48598,7 @@
         <v>46252</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48670,7 +48671,7 @@
         <v>46206</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48748,7 +48749,7 @@
         <v>45628</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -48821,7 +48822,7 @@
         <v>46253</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -48899,7 +48900,7 @@
         <v>45188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -48972,7 +48973,7 @@
         <v>46254</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49045,7 +49046,7 @@
         <v>46254</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49123,7 +49124,7 @@
         <v>46213</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49201,7 +49202,7 @@
         <v>46213</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49274,7 +49275,7 @@
         <v>44577</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49347,7 +49348,7 @@
         <v>44675</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49425,7 +49426,7 @@
         <v>46213</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49503,7 +49504,7 @@
         <v>46213</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49576,7 +49577,7 @@
         <v>46258</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49654,7 +49655,7 @@
         <v>45125</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49727,7 +49728,7 @@
         <v>46258</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -49805,7 +49806,7 @@
         <v>45061</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -49878,7 +49879,7 @@
         <v>44822</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -49951,7 +49952,7 @@
         <v>46213</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50029,7 +50030,7 @@
         <v>46213</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50107,7 +50108,7 @@
         <v>45097</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50180,7 +50181,7 @@
         <v>46213</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50253,7 +50254,7 @@
         <v>45173</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50326,7 +50327,7 @@
         <v>45177</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50404,7 +50405,7 @@
         <v>45685</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50477,7 +50478,7 @@
         <v>45523</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50550,7 +50551,7 @@
         <v>46260</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50628,7 +50629,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50706,7 +50707,7 @@
         <v>46260</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50784,7 +50785,7 @@
         <v>46260</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -50857,7 +50858,7 @@
         <v>46219</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -50930,7 +50931,7 @@
         <v>46219</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51008,7 +51009,7 @@
         <v>45265</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51081,7 +51082,7 @@
         <v>46219</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51159,7 +51160,7 @@
         <v>46219</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51237,7 +51238,7 @@
         <v>46219</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51310,7 +51311,7 @@
         <v>45158</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51383,7 +51384,7 @@
         <v>46219</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51456,7 +51457,7 @@
         <v>45194</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51529,7 +51530,7 @@
         <v>45233</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51607,7 +51608,7 @@
         <v>45749</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51680,7 +51681,7 @@
         <v>45749</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51753,7 +51754,7 @@
         <v>45305</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -51826,7 +51827,7 @@
         <v>46220</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -51904,7 +51905,7 @@
         <v>46220</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -51982,7 +51983,7 @@
         <v>46265</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52060,7 +52061,7 @@
         <v>45229</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52133,7 +52134,7 @@
         <v>46265</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52211,7 +52212,7 @@
         <v>46038</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52284,7 +52285,7 @@
         <v>46038</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52357,7 +52358,7 @@
         <v>45756</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52430,7 +52431,7 @@
         <v>46265</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52508,7 +52509,7 @@
         <v>46265</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52586,7 +52587,7 @@
         <v>46220</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52664,7 +52665,7 @@
         <v>46220</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52742,7 +52743,7 @@
         <v>46220</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -52820,7 +52821,7 @@
         <v>45227</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -52893,7 +52894,7 @@
         <v>45357</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -52971,7 +52972,7 @@
         <v>45254</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53049,7 +53050,7 @@
         <v>45768</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53122,7 +53123,7 @@
         <v>45440</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53195,7 +53196,7 @@
         <v>44753</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53268,7 +53269,7 @@
         <v>45369</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53341,7 +53342,7 @@
         <v>46191</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53419,7 +53420,7 @@
         <v>46230</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53492,7 +53493,7 @@
         <v>46272</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53570,7 +53571,7 @@
         <v>46268</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53643,7 +53644,7 @@
         <v>45310</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53716,7 +53717,7 @@
         <v>45477</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53789,7 +53790,7 @@
         <v>45274</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -53862,7 +53863,7 @@
         <v>45729</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -53935,7 +53936,7 @@
         <v>46272</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54008,7 +54009,7 @@
         <v>44803</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54081,7 +54082,7 @@
         <v>45265</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54154,7 +54155,7 @@
         <v>46276</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54232,7 +54233,7 @@
         <v>46276</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54310,7 +54311,7 @@
         <v>45272</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54383,7 +54384,7 @@
         <v>45079</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54461,7 +54462,7 @@
         <v>45079</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54539,7 +54540,7 @@
         <v>45736</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54612,7 +54613,7 @@
         <v>46276</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54685,7 +54686,7 @@
         <v>45684</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54758,7 +54759,7 @@
         <v>46279</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -54831,7 +54832,7 @@
         <v>45257</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -54904,7 +54905,7 @@
         <v>45082</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -54982,7 +54983,7 @@
         <v>45097</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55055,7 +55056,7 @@
         <v>46191</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55133,7 +55134,7 @@
         <v>46191</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55211,7 +55212,7 @@
         <v>44546</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55284,7 +55285,7 @@
         <v>45229</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55357,7 +55358,7 @@
         <v>46285</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55435,7 +55436,7 @@
         <v>46285</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55513,7 +55514,7 @@
         <v>46286</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55591,7 +55592,7 @@
         <v>45048</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55664,7 +55665,7 @@
         <v>45047</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55737,7 +55738,7 @@
         <v>45471</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -55810,7 +55811,7 @@
         <v>46285</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -55888,7 +55889,7 @@
         <v>46285</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -55966,7 +55967,7 @@
         <v>45547</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56039,7 +56040,7 @@
         <v>44473</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56112,7 +56113,7 @@
         <v>46283</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56185,7 +56186,7 @@
         <v>45974</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56258,7 +56259,7 @@
         <v>45954</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56336,7 +56337,7 @@
         <v>45008</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56414,7 +56415,7 @@
         <v>46245</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56492,7 +56493,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56565,7 +56566,7 @@
         <v>46287</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56638,7 +56639,7 @@
         <v>44895</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56711,7 +56712,7 @@
         <v>44916</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -56784,7 +56785,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -56862,7 +56863,7 @@
         <v>44979</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -56935,7 +56936,7 @@
         <v>45575</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57013,7 +57014,7 @@
         <v>46287</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57086,7 +57087,7 @@
         <v>45166</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57164,7 +57165,7 @@
         <v>45404</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57242,7 +57243,7 @@
         <v>44902</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57315,7 +57316,7 @@
         <v>45107</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57388,7 +57389,7 @@
         <v>45189</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57461,7 +57462,7 @@
         <v>45478</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57539,7 +57540,7 @@
         <v>46247</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57617,7 +57618,7 @@
         <v>46290</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57695,7 +57696,7 @@
         <v>46248</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57768,7 +57769,7 @@
         <v>44853</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -57841,7 +57842,7 @@
         <v>45497</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -57914,7 +57915,7 @@
         <v>44906</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -57987,7 +57988,7 @@
         <v>45237</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58060,7 +58061,7 @@
         <v>45474</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58138,7 +58139,7 @@
         <v>45610</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58211,7 +58212,7 @@
         <v>44577</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58284,7 +58285,7 @@
         <v>45618</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58362,7 +58363,7 @@
         <v>45211</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58440,7 +58441,7 @@
         <v>44721</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58513,7 +58514,7 @@
         <v>45119</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58591,7 +58592,7 @@
         <v>45453</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58669,7 +58670,7 @@
         <v>44734</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58742,7 +58743,7 @@
         <v>44946</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -58815,7 +58816,7 @@
         <v>44958</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -58888,7 +58889,7 @@
         <v>44978</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -58961,7 +58962,7 @@
         <v>44846</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59034,7 +59035,7 @@
         <v>45590</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59107,7 +59108,7 @@
         <v>45254</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59185,7 +59186,7 @@
         <v>45762</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59258,7 +59259,7 @@
         <v>45074</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59331,7 +59332,7 @@
         <v>44868</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59409,7 +59410,7 @@
         <v>45189</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59482,7 +59483,7 @@
         <v>45575</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59555,7 +59556,7 @@
         <v>45471</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59628,7 +59629,7 @@
         <v>45057</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59701,7 +59702,7 @@
         <v>44865</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -59774,7 +59775,7 @@
         <v>45303</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -59847,7 +59848,7 @@
         <v>45523</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -59920,7 +59921,7 @@
         <v>45667</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -59998,7 +59999,7 @@
         <v>45170</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60076,7 +60077,7 @@
         <v>45103</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60149,7 +60150,7 @@
         <v>45036</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60222,7 +60223,7 @@
         <v>45072</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60300,7 +60301,7 @@
         <v>44902</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60373,7 +60374,7 @@
         <v>45611</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60446,7 +60447,7 @@
         <v>45043</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60519,7 +60520,7 @@
         <v>45604</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60592,7 +60593,7 @@
         <v>45525</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60665,7 +60666,7 @@
         <v>45532</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -60738,7 +60739,7 @@
         <v>45183</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -60811,7 +60812,7 @@
         <v>45664</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -60884,7 +60885,7 @@
         <v>44833</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -60957,7 +60958,7 @@
         <v>45568</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61035,7 +61036,7 @@
         <v>45341</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61113,7 +61114,7 @@
         <v>45334</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61186,7 +61187,7 @@
         <v>45273</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61259,7 +61260,7 @@
         <v>45218</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61337,7 +61338,7 @@
         <v>45462</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61410,7 +61411,7 @@
         <v>45516</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61483,7 +61484,7 @@
         <v>45568</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61561,7 +61562,7 @@
         <v>44984</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61634,7 +61635,7 @@
         <v>45111</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -61707,7 +61708,7 @@
         <v>45471</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -61780,7 +61781,7 @@
         <v>45714</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -61853,7 +61854,7 @@
         <v>45103</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -61926,7 +61927,7 @@
         <v>45729</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -61999,7 +62000,7 @@
         <v>45439</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62072,7 +62073,7 @@
         <v>45702</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62145,7 +62146,7 @@
         <v>45538</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62223,7 +62224,7 @@
         <v>45384</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62296,7 +62297,7 @@
         <v>45400</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62374,7 +62375,7 @@
         <v>45702</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62447,7 +62448,7 @@
         <v>45776</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62520,7 +62521,7 @@
         <v>45777</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62598,7 +62599,7 @@
         <v>45777</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62676,7 +62677,7 @@
         <v>45783</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -62749,7 +62750,7 @@
         <v>45509</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -62822,7 +62823,7 @@
         <v>45567</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -62895,7 +62896,7 @@
         <v>45460</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -62968,7 +62969,7 @@
         <v>45569</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63041,7 +63042,7 @@
         <v>45253</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63119,7 +63120,7 @@
         <v>45203</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63192,7 +63193,7 @@
         <v>45267</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63270,7 +63271,7 @@
         <v>45537</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63348,7 +63349,7 @@
         <v>45229</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63426,7 +63427,7 @@
         <v>45537</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63504,7 +63505,7 @@
         <v>45618</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63577,7 +63578,7 @@
         <v>45546</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63650,7 +63651,7 @@
         <v>45181</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -63728,7 +63729,7 @@
         <v>45639</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -63801,7 +63802,7 @@
         <v>45418</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -63874,7 +63875,7 @@
         <v>45440</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -63947,7 +63948,7 @@
         <v>45667</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64025,7 +64026,7 @@
         <v>44172</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64103,7 +64104,7 @@
         <v>44246</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64181,7 +64182,7 @@
         <v>44172</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64259,7 +64260,7 @@
         <v>45578</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64332,7 +64333,7 @@
         <v>45218</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64410,7 +64411,7 @@
         <v>45040</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64483,7 +64484,7 @@
         <v>45716</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64561,7 +64562,7 @@
         <v>45777</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64639,7 +64640,7 @@
         <v>45714</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -64712,7 +64713,7 @@
         <v>45832</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -64790,7 +64791,7 @@
         <v>45980</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -64868,7 +64869,7 @@
         <v>46094</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -64946,7 +64947,7 @@
         <v>46111</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65019,7 +65020,7 @@
         <v>46128</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65097,7 +65098,7 @@
         <v>46245</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>46064</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45138</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45967</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46260</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45138</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>46289</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>46289</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>46148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>46276</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>46191</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>46191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45568</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45099</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45905</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45940</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>46285</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44472</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>46038</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>46142</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>46191</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>46289</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>46289</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>46293</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45936</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>46174</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44484</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45068</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>45980</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>46125</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>46175</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>46239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>46293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>46064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46108</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45393</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>46191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>46272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46289</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>46245</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46289</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>46289</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>46174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44484</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45218</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44693</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44691</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44679</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45937</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45376</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45946</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45946</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45946</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44949</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45980</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>46112</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>46112</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>46125</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>46128</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>46128</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44522</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45537</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>44970</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>46146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>46157</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>46162</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45698</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45272</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45007</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45411</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44536</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46276</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46191</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45250</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>46191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45218</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45104</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46293</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46293</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46293</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45471</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45698</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>44564</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45391</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45698</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44853</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>44484</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44508</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44613</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44722</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>44577</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>44481</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44638</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>44714</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44627</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44790</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44676</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>44630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44862</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44603</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44713</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44671</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44577</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44505</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44671</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44546</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>44823</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>44522</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44484</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44505</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44490</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>44694</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44629</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44665</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>44487</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44497</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44819</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44672</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44825</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44622</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>44875</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44491</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44526</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>44602</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>44777</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44665</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44502</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44502</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44481</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>44491</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>44784</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44536</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>44860</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44873</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44536</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44539</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>44539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44608</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>44650</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44479</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>44636</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>44618</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>44490</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44698</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44784</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45310</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45736</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45518</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45530</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45439</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>44531</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45107</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44683</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45611</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44967</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45604</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44943</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45054</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45384</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45158</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45183</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45194</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45646</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45074</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45575</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45488</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45140</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45751</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45537</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44853</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45884</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45075</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45310</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45305</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45097</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>46002</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45344</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45330</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45982</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45982</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>45639</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45608</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45749</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>45181</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45418</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45243</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45610</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45243</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45243</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>46009</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45177</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45541</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45618</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45749</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45272</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45667</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45887</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45546</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45440</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45889</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45749</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44988</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45497</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>44803</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45369</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46030</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>46035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45903</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45433</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46037</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44888</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44928</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46038</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45108</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45793</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45456</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45795</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45155</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45244</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45796</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46044</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45173</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45796</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45796</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45456</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45590</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45168</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45441</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45441</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>46049</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>44979</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45925</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45645</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>46057</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46056</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>44480</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>46058</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45201</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45201</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45518</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45547</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45048</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44574</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>45610</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>44551</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>46071</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>44675</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45940</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45940</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45940</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44865</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45947</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45946</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45103</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44546</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45194</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>44908</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>45471</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45952</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45471</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45148</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45152</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45189</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44577</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44900</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44503</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45964</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44553</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45131</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45968</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45227</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45384</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45974</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>46101</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>45974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45091</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45201</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45538</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45257</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45265</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>46108</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45980</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45980</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45980</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46108</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45119</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45348</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45729</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45821</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45488</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45316</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46115</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45393</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46115</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>46115</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46115</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46115</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46115</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46115</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46115</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45222</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46121</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>44949</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>44895</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>46126</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45323</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>46125</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45995</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>46128</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45995</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44990</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45357</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46128</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>46128</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45523</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45769</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45072</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>46133</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45477</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45832</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45832</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44577</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45077</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45832</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45832</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45835</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>44846</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>44594</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45791</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45516</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45265</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45932</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45845</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45520</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45139</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45538</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45832</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45845</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45614</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>44522</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45343</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45684</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45134</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45237</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44728</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45694</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>44978</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>44868</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>45670</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44990</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44946</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45400</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45173</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44902</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45642</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45099</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45685</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45832</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45586</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45097</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45093</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45548</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>44791</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45915</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>45440</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45559</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45646</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45341</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45534</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45565</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45714</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45575</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45229</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45538</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45252</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>46142</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>44511</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45229</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>44602</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45877</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45229</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45565</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45303</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45471</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>44734</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>44906</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45831</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45047</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45943</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45817</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>46034</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45568</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>44984</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45273</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>46157</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>46157</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>46157</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>46160</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45394</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>46161</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>46161</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46161</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>46161</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>46161</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46160</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>46161</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>45804</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>45874</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>46161</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46161</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>46161</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45618</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>46161</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>46161</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>46162</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45355</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>45702</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46167</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45876</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>46167</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>44979</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45880</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46139</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>44958</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>45554</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46170</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>46170</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>46170</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45694</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46171</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45751</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45233</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46174</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>44981</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46175</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>45538</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>46175</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45005</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45005</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45884</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45628</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45404</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>44546</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45768</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45194</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>44721</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44876</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45057</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45145</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45166</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45338</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>46189</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>46189</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>46189</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45726</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45159</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45103</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45061</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45279</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45575</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45523</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>44833</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         <v>46190</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44927</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>45575</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>46191</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46191</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45952</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>46191</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45274</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>46191</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>46191</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>46191</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>46191</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>46191</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45149</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45523</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45766</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45600</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45036</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>46198</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45478</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46198</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45518</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45518</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
         <v>45518</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45548</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>46203</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51061,7 +51061,7 @@
         <v>45125</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>45113</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>46203</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46203</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44841</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45061</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45170</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45562</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45474</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>46206</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45511</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>44978</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>46206</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44963</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>46206</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45005</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>45034</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46213</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>46213</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45582</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>46213</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>46213</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>46258</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>46258</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>46213</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>46213</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45635</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>46213</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53175,7 +53175,7 @@
         <v>46260</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53248,7 +53248,7 @@
         <v>44740</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>46260</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         <v>46220</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>46220</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>46219</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45194</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>46265</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>46265</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>46220</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>46220</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45628</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54091,7 +54091,7 @@
         <v>46265</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>46219</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>46219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>46038</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>46265</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54466,7 +54466,7 @@
         <v>46220</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54544,7 +54544,7 @@
         <v>46038</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>46219</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54690,7 +54690,7 @@
         <v>46219</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>46219</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45756</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45702</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45218</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45590</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>46268</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55216,7 +55216,7 @@
         <v>46230</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>46272</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>46272</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55440,7 +55440,7 @@
         <v>46191</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45072</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46276</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45537</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>46279</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45519</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>46191</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>46191</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45412</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45387</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45387</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45082</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>45141</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45400</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>44970</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45194</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>44866</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45538</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>46283</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>44621</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45974</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45954</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46286</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45009</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>44566</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>46287</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>46285</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>46287</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         <v>45667</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>45667</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57690,7 +57690,7 @@
         <v>46285</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45575</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57841,7 +57841,7 @@
         <v>44602</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>46285</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45103</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45511</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58138,7 +58138,7 @@
         <v>44735</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>46245</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>45111</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>46287</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58440,7 +58440,7 @@
         <v>44883</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45254</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>45525</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>46287</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45177</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46293</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45251</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>45726</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45393</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45762</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59190,7 +59190,7 @@
         <v>45107</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>44902</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>45519</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>46293</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45107</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>46293</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>46290</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>46293</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59804,7 +59804,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>46248</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>46293</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60111,7 +60111,7 @@
         <v>44822</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45274</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60257,7 +60257,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60335,7 +60335,7 @@
         <v>45254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>45736</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45095</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45571</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>44916</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60710,7 +60710,7 @@
         <v>45170</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>46252</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45546</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60939,7 +60939,7 @@
         <v>45211</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61017,7 +61017,7 @@
         <v>44544</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61090,7 +61090,7 @@
         <v>46247</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61168,7 +61168,7 @@
         <v>46254</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61246,7 +61246,7 @@
         <v>44473</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61319,7 +61319,7 @@
         <v>45471</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>46296</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>46254</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>46253</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61616,7 +61616,7 @@
         <v>46296</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61694,7 +61694,7 @@
         <v>46296</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61767,7 +61767,7 @@
         <v>45645</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45189</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45372</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45079</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>45079</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
         <v>45462</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62220,7 +62220,7 @@
         <v>45575</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62298,7 +62298,7 @@
         <v>45441</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>45553</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45729</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45008</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45113</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45095</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45377</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>45664</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>45274</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>45280</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63043,7 +63043,7 @@
         <v>44890</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         <v>45334</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63189,7 +63189,7 @@
         <v>45516</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63262,7 +63262,7 @@
         <v>44753</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45251</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63408,7 +63408,7 @@
         <v>45643</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63481,7 +63481,7 @@
         <v>45569</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>45618</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>45119</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>44946</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>44809</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63856,7 +63856,7 @@
         <v>45264</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45702</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64002,7 +64002,7 @@
         <v>45219</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>44665</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64153,7 +64153,7 @@
         <v>45211</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>45453</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64304,7 +64304,7 @@
         <v>45777</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64382,7 +64382,7 @@
         <v>45777</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45776</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45783</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>45567</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64679,7 +64679,7 @@
         <v>45509</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64752,7 +64752,7 @@
         <v>45460</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64825,7 +64825,7 @@
         <v>45569</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64898,7 +64898,7 @@
         <v>45253</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>45203</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>45229</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65127,7 +65127,7 @@
         <v>45267</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>45537</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>44172</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65361,7 +65361,7 @@
         <v>44172</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65439,7 +65439,7 @@
         <v>44246</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65517,7 +65517,7 @@
         <v>45578</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         <v>45218</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45040</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65741,7 +65741,7 @@
         <v>45716</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>45777</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65897,7 +65897,7 @@
         <v>45714</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65970,7 +65970,7 @@
         <v>45832</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66048,7 +66048,7 @@
         <v>45980</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>46094</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>46111</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>46128</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>46245</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66433,7 +66433,7 @@
         <v>46296</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>46064</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>45138</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45967</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46260</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>46203</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>46174</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45138</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>46289</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>46289</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>46148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>46276</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>46191</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>46191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45905</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         <v>45568</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45021</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45099</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45905</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45940</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45099</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>46285</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44472</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>46038</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45952</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>46141</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>46142</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>46191</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>46289</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>46289</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>46293</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45936</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>46174</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>44484</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45068</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>45980</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>46125</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>46175</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>46239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>46293</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>46064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>46108</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45393</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>46191</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>46272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>46191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46289</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>46245</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>46289</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>46289</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>46174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>44484</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45218</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44512</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44693</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44691</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44679</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45937</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45943</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45376</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45946</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>45946</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45946</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45946</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44949</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>45980</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>45281</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45980</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45138</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>46112</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>46112</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>46125</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>46128</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>46128</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45832</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44820</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44522</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>45537</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>44970</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>46146</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>46150</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>46157</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>46162</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45698</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45272</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45007</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45411</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44536</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>46276</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46191</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45250</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>46191</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45218</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45104</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
         <v>46293</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>46293</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46293</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45471</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17014,7 +17014,7 @@
         <v>45698</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>44564</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45391</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45698</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>44853</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44495</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>44484</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44508</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44503</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44613</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>44721</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44722</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>44577</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>44862</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>44481</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44754</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44638</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>44714</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44627</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44790</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44676</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>44630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44862</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>44603</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44713</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44671</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>44706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44577</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>44505</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44671</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>44546</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>44823</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>44522</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>44635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>44484</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>44505</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>44490</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>44694</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>44629</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44665</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44594</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>44487</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>44497</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44819</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>44672</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44825</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>44622</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>44875</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44491</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44526</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>44889</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>44602</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>44777</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>44665</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>44502</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>44502</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>44481</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>44491</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>44784</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44536</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>44860</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44873</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44536</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>44539</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>44539</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>44608</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>44650</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44479</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>44636</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>44618</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>44511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>44490</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44698</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44784</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45310</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45736</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45518</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>45530</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45439</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>44531</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45107</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44683</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45611</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>44974</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44967</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45604</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45030</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>44943</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45054</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45384</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45158</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45183</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45194</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45646</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45074</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45575</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45488</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45140</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45751</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45537</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44853</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>45884</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45075</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45310</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45305</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45097</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>46002</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45344</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45330</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25737,7 +25737,7 @@
         <v>45982</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25810,7 +25810,7 @@
         <v>45982</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>45639</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45608</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45749</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>45181</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>45418</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45243</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45610</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>45243</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>45243</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>46009</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26633,7 +26633,7 @@
         <v>45177</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26711,7 +26711,7 @@
         <v>45541</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45618</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45749</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45272</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45667</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45887</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45546</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45440</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45889</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45889</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27539,7 +27539,7 @@
         <v>45749</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>44988</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45497</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>44803</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>45369</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46030</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>46035</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45903</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45162</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45433</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>46037</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44888</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>44928</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>44902</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46038</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45108</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45793</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45456</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45795</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45155</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45244</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45796</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>46044</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45173</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>45796</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45796</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29472,7 +29472,7 @@
         <v>45456</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45590</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>45168</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>45441</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45441</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29847,7 +29847,7 @@
         <v>46049</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>44979</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45925</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>45645</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>46057</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>46056</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>44480</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>46058</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45201</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45201</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45518</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>45547</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45048</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44574</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30889,7 +30889,7 @@
         <v>45610</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45937</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31040,7 +31040,7 @@
         <v>44551</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31113,7 +31113,7 @@
         <v>46071</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>44675</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45940</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45940</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45940</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>44865</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45947</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45946</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31873,7 +31873,7 @@
         <v>45103</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>44546</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32019,7 +32019,7 @@
         <v>45194</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>44908</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32165,7 +32165,7 @@
         <v>45471</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45952</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45471</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32384,7 +32384,7 @@
         <v>45148</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45152</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45189</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44577</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>44900</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45099</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44503</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45964</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44553</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>44951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33124,7 +33124,7 @@
         <v>45131</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>45188</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45968</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45227</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>46098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>45384</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45974</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33879,7 +33879,7 @@
         <v>46101</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33952,7 +33952,7 @@
         <v>45974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45091</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45201</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45538</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45257</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45265</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>46108</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45980</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45980</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45979</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45980</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46108</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45119</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45348</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45729</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45821</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45488</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46113</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>46114</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45316</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46115</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>45393</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46115</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>46115</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46115</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46115</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46115</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46115</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>46115</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36343,7 +36343,7 @@
         <v>45222</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>46121</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         <v>44949</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>44895</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>46126</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36708,7 +36708,7 @@
         <v>45323</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>46125</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45995</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>46128</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45995</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>44990</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37151,7 +37151,7 @@
         <v>45357</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46128</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         <v>46128</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45523</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37536,7 +37536,7 @@
         <v>45769</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45072</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>46133</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45477</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>45832</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>45832</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>44577</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38062,7 +38062,7 @@
         <v>45077</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45832</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45832</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45835</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>44846</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>44594</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45791</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45516</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45265</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45932</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45845</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45520</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39041,7 +39041,7 @@
         <v>45139</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39119,7 +39119,7 @@
         <v>45538</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39197,7 +39197,7 @@
         <v>45832</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>45845</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45614</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>44522</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>45343</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45684</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>45134</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>45237</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>44728</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45694</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>44978</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>44868</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>45670</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44990</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>45952</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>44946</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45400</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45173</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>44902</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45642</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45099</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>45685</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>45832</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45586</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45097</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45093</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45548</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>44791</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45915</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>45440</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45559</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45646</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41651,7 +41651,7 @@
         <v>45341</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45534</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45565</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45714</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45575</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45229</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45538</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42255,7 +42255,7 @@
         <v>45252</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42328,7 +42328,7 @@
         <v>46142</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42406,7 +42406,7 @@
         <v>44511</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45229</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>44602</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45877</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45229</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45565</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45303</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45471</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>44734</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>44906</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45831</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45047</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45943</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45817</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>46034</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>45568</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>44984</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45273</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         <v>46157</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>46157</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>46157</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>46160</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44037,7 +44037,7 @@
         <v>45394</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>46161</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>46161</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46161</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>46161</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>46161</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>46160</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44573,7 +44573,7 @@
         <v>46161</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>45804</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44724,7 +44724,7 @@
         <v>45874</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>46161</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46161</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>46161</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45618</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>46161</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45192,7 +45192,7 @@
         <v>46161</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>46162</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45348,7 +45348,7 @@
         <v>45355</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45421,7 +45421,7 @@
         <v>45702</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45494,7 +45494,7 @@
         <v>46167</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45572,7 +45572,7 @@
         <v>45876</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>46167</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45723,7 +45723,7 @@
         <v>46167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>44979</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>45880</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>46139</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>44958</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>45554</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>45043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46170</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>46170</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>46170</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>45694</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46171</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45751</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45233</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>46174</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46848,7 +46848,7 @@
         <v>44981</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46175</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46999,7 +46999,7 @@
         <v>45538</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>46175</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45005</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47228,7 +47228,7 @@
         <v>45005</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45884</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45628</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         <v>45404</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>44546</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>45768</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45194</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>44721</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>44876</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45057</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47973,7 +47973,7 @@
         <v>45145</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45166</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45338</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48275,7 +48275,7 @@
         <v>46189</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48348,7 +48348,7 @@
         <v>46189</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>46189</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>45726</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45159</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45103</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>45061</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48786,7 +48786,7 @@
         <v>45279</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45575</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>45523</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>44833</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49083,7 +49083,7 @@
         <v>46190</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44927</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>45575</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49307,7 +49307,7 @@
         <v>46191</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49385,7 +49385,7 @@
         <v>46191</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49463,7 +49463,7 @@
         <v>45952</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49541,7 +49541,7 @@
         <v>46191</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45274</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49692,7 +49692,7 @@
         <v>46191</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49770,7 +49770,7 @@
         <v>46191</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>46191</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>46191</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>46191</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50082,7 +50082,7 @@
         <v>45149</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45523</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45766</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45600</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45036</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>46198</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45478</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>46198</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45518</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45518</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50832,7 +50832,7 @@
         <v>45518</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45548</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>46203</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51061,7 +51061,7 @@
         <v>45125</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>45113</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>46203</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46203</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44841</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>45061</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45170</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45562</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45474</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>46206</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45511</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         <v>44978</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>46206</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52040,7 +52040,7 @@
         <v>44963</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52113,7 +52113,7 @@
         <v>46206</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45005</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>45034</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>46213</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>46213</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45582</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52566,7 +52566,7 @@
         <v>46213</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52644,7 +52644,7 @@
         <v>46213</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52717,7 +52717,7 @@
         <v>46258</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>46258</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52873,7 +52873,7 @@
         <v>46213</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52946,7 +52946,7 @@
         <v>46213</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45635</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53097,7 +53097,7 @@
         <v>46213</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53175,7 +53175,7 @@
         <v>46260</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53248,7 +53248,7 @@
         <v>44740</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53321,7 +53321,7 @@
         <v>46260</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53399,7 +53399,7 @@
         <v>46220</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>46220</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>46219</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45194</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>46265</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>46265</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>46220</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>46220</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54018,7 +54018,7 @@
         <v>45628</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54091,7 +54091,7 @@
         <v>46265</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54169,7 +54169,7 @@
         <v>46219</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>46219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>46038</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>46265</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54466,7 +54466,7 @@
         <v>46220</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54544,7 +54544,7 @@
         <v>46038</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>46219</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54690,7 +54690,7 @@
         <v>46219</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54768,7 +54768,7 @@
         <v>46219</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54846,7 +54846,7 @@
         <v>45756</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45702</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>45218</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>45590</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55143,7 +55143,7 @@
         <v>46268</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55216,7 +55216,7 @@
         <v>46230</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55289,7 +55289,7 @@
         <v>46272</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55362,7 +55362,7 @@
         <v>46272</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55440,7 +55440,7 @@
         <v>46191</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45072</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>46276</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45537</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>46279</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45519</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>46191</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>46191</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56049,7 +56049,7 @@
         <v>45412</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>45387</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45387</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56268,7 +56268,7 @@
         <v>45082</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>45141</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>45400</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56497,7 +56497,7 @@
         <v>44970</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56570,7 +56570,7 @@
         <v>45194</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56643,7 +56643,7 @@
         <v>44866</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45538</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56789,7 +56789,7 @@
         <v>46283</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>44621</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45974</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45954</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46286</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45009</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>44566</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>46287</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>46285</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>46287</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         <v>45667</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         <v>45667</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57690,7 +57690,7 @@
         <v>46285</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57768,7 +57768,7 @@
         <v>45575</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57841,7 +57841,7 @@
         <v>44602</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>46285</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57992,7 +57992,7 @@
         <v>45103</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58065,7 +58065,7 @@
         <v>45511</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58138,7 +58138,7 @@
         <v>44735</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58216,7 +58216,7 @@
         <v>46245</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58294,7 +58294,7 @@
         <v>45111</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>46287</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58440,7 +58440,7 @@
         <v>44883</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58513,7 +58513,7 @@
         <v>45254</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58591,7 +58591,7 @@
         <v>45525</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58664,7 +58664,7 @@
         <v>46287</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58737,7 +58737,7 @@
         <v>45177</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>46293</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>45251</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58966,7 +58966,7 @@
         <v>45726</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45393</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45762</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59190,7 +59190,7 @@
         <v>45107</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59263,7 +59263,7 @@
         <v>44902</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59336,7 +59336,7 @@
         <v>45519</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59414,7 +59414,7 @@
         <v>46293</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45107</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>46293</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>46290</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59726,7 +59726,7 @@
         <v>46293</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59804,7 +59804,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>46248</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>46293</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>46293</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60111,7 +60111,7 @@
         <v>44822</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60184,7 +60184,7 @@
         <v>45274</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60257,7 +60257,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60335,7 +60335,7 @@
         <v>45254</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60413,7 +60413,7 @@
         <v>45736</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45095</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45571</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60637,7 +60637,7 @@
         <v>44916</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60710,7 +60710,7 @@
         <v>45170</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>46252</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>45546</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60939,7 +60939,7 @@
         <v>45211</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61017,7 +61017,7 @@
         <v>44544</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61090,7 +61090,7 @@
         <v>46247</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61168,7 +61168,7 @@
         <v>46254</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61246,7 +61246,7 @@
         <v>44473</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61319,7 +61319,7 @@
         <v>45471</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61392,7 +61392,7 @@
         <v>46296</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>46254</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>46253</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61616,7 +61616,7 @@
         <v>46296</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61694,7 +61694,7 @@
         <v>46296</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61767,7 +61767,7 @@
         <v>45645</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45189</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45372</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45079</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>45079</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62147,7 +62147,7 @@
         <v>45462</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62220,7 +62220,7 @@
         <v>45575</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62298,7 +62298,7 @@
         <v>45441</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>45553</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62449,7 +62449,7 @@
         <v>45729</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45008</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62600,7 +62600,7 @@
         <v>45113</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62673,7 +62673,7 @@
         <v>45095</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62746,7 +62746,7 @@
         <v>45377</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62819,7 +62819,7 @@
         <v>45664</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>45274</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62965,7 +62965,7 @@
         <v>45280</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63043,7 +63043,7 @@
         <v>44890</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63116,7 +63116,7 @@
         <v>45334</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63189,7 +63189,7 @@
         <v>45516</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63262,7 +63262,7 @@
         <v>44753</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45251</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63408,7 +63408,7 @@
         <v>45643</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63481,7 +63481,7 @@
         <v>45569</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63554,7 +63554,7 @@
         <v>45618</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63632,7 +63632,7 @@
         <v>45119</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>44946</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>44809</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63856,7 +63856,7 @@
         <v>45264</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45702</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -64002,7 +64002,7 @@
         <v>45219</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64080,7 +64080,7 @@
         <v>44665</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64153,7 +64153,7 @@
         <v>45211</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>45453</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64304,7 +64304,7 @@
         <v>45777</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64382,7 +64382,7 @@
         <v>45777</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45776</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64533,7 +64533,7 @@
         <v>45783</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64606,7 +64606,7 @@
         <v>45567</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64679,7 +64679,7 @@
         <v>45509</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64752,7 +64752,7 @@
         <v>45460</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64825,7 +64825,7 @@
         <v>45569</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64898,7 +64898,7 @@
         <v>45253</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>45203</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>45229</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65127,7 +65127,7 @@
         <v>45267</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65205,7 +65205,7 @@
         <v>45537</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>44172</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65361,7 +65361,7 @@
         <v>44172</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65439,7 +65439,7 @@
         <v>44246</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65517,7 +65517,7 @@
         <v>45578</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65590,7 +65590,7 @@
         <v>45218</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45040</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65741,7 +65741,7 @@
         <v>45716</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>45777</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65897,7 +65897,7 @@
         <v>45714</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65970,7 +65970,7 @@
         <v>45832</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66048,7 +66048,7 @@
         <v>45980</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66126,7 +66126,7 @@
         <v>46094</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>46111</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>46128</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>46245</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66433,7 +66433,7 @@
         <v>46296</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45138</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45905</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45967</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>46260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>46260</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45138</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>46289</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>46289</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>46148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>46276</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>46191</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>46191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45568</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45905</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46191</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45905</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45940</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46285</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>46260</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>46038</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45952</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46141</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>46142</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>46191</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>46289</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>46289</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>46293</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45936</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>46293</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46174</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44484</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45980</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45068</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46150</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46175</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>46239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45905</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45393</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>46064</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46108</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>46191</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>46272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>46289</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>46289</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>46289</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>46245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44512</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44679</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44564</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45698</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45698</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45698</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45411</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45645</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45104</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45218</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45922</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44949</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45946</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45537</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45138</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45980</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45980</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44970</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45471</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>46112</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46112</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>46125</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>46128</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>46128</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45281</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>44820</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45376</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44522</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>46150</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>46162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46276</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>46191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45250</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>46191</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>46293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>46293</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>46293</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45698</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45391</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45698</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44853</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44495</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>44508</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44484</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>44503</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44613</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44721</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44722</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44577</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>44862</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44481</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44754</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44638</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44627</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>44790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44676</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44603</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>44862</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44671</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44706</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44671</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44577</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44505</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44546</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44823</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44522</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44622</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44694</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44484</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44875</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44505</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44873</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>44491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44490</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44665</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44629</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44777</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44608</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>44665</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>44502</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44502</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44594</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44526</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44481</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44487</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44650</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44497</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>44479</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44618</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44733</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44636</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44672</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44536</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>44825</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45355</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45412</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45189</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45264</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45091</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45393</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44490</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>44698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>44784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>44928</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45575</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>44927</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45618</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45471</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45338</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45222</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45433</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45384</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>44865</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45303</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45194</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45523</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45667</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45243</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45243</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45243</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44890</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45316</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45471</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45103</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45751</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45108</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45036</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45751</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45702</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45518</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45072</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44809</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>44876</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>44902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45103</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45611</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44866</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45043</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45107</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45694</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45604</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45884</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45525</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45532</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44902</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45323</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44531</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45183</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45664</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44833</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45884</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>45112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45568</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45341</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45334</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45274</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45152</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45887</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45518</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45134</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45575</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45273</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45279</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45519</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45537</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44883</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45889</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45107</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45218</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45889</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>45462</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45516</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45538</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45441</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45441</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45568</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44984</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45111</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45005</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45005</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45488</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45471</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44978</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45586</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45714</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45103</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45729</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45441</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45903</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44602</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45005</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45608</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45439</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44602</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45546</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>45702</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45538</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45538</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45384</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45400</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44551</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44480</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45289</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44981</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>45702</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45776</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45141</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45777</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45777</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45393</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45726</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45571</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44544</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45518</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45518</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45643</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45783</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45509</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45645</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45567</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45460</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45280</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45541</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45519</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45140</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44908</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45569</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45749</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45203</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45267</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44574</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45537</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45229</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45170</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>44553</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45537</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45618</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44594</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45343</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45400</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45546</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45219</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45925</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45330</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45181</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45639</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45201</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45177</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45565</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45418</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44888</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45440</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45562</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45667</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45565</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45796</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45553</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>44522</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45795</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45796</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45796</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44621</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44949</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45054</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45218</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44943</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45244</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45456</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45793</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44979</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45590</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45201</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45201</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45155</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45456</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45229</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45194</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>44740</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45131</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45310</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45394</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>44683</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45582</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45769</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45667</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45610</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>45173</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45387</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45387</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45937</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45377</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45548</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45168</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45569</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45372</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45813</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45937</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45095</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45095</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45628</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45251</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44963</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45940</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45940</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45940</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45188</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44735</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45266</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>44967</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>44970</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>44577</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45348</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>44675</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45125</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45099</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45061</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44822</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45821</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45097</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45947</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45173</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45635</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45952</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45177</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45685</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45628</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45827</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>45344</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45523</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45523</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45832</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45832</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45832</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45832</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45034</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45194</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45964</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45009</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44503</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45835</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45145</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45159</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45158</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45516</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45488</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45194</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45538</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45511</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45968</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45511</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44951</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45233</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45520</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45749</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45749</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45305</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45845</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45845</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45229</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45756</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45974</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45974</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45694</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>44728</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45670</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>44665</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45149</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45646</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45170</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45072</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45227</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45357</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>44546</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45113</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>45254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45768</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45440</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>44990</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>44753</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45575</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>45369</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45534</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45530</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45980</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45030</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45980</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45310</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45477</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45874</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45274</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45194</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45979</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45980</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>45980</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>45729</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44803</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45876</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>44900</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45265</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45880</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>44511</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45272</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45079</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45079</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45766</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45736</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45211</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45684</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>46098</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44566</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46101</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>44990</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45257</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45097</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45251</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45736</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45077</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45075</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>46108</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>46108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>44546</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45229</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>46108</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>46113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>44946</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45048</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45047</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45471</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>46115</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>46115</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>46114</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>46114</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>46115</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>46115</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>46115</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>46115</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>46115</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45547</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>46115</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>46121</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45995</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45995</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>46125</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45008</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>46126</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>46128</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>46128</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>46002</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>44895</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>46133</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>44916</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>44979</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45575</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>45166</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>45982</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45832</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45982</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45404</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>44902</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51314,7 +51314,7 @@
         <v>45538</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>46009</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45107</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46013</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>45189</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45478</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45791</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>44853</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         <v>45497</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45915</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>44906</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52127,7 +52127,7 @@
         <v>45139</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>45237</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>46030</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45932</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45252</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52497,7 +52497,7 @@
         <v>45474</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45610</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>44577</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45952</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45618</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45642</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45614</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>46035</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>46037</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46038</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45211</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>45559</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>44721</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53471,7 +53471,7 @@
         <v>45119</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45453</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         <v>44734</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>46044</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53773,7 +53773,7 @@
         <v>45832</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>44946</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>44958</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>44978</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>44846</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45590</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>45254</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>45762</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>46049</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54440,7 +54440,7 @@
         <v>45074</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54513,7 +54513,7 @@
         <v>44868</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54591,7 +54591,7 @@
         <v>45093</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>46142</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>46056</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>46058</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>44791</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45106</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46071</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45877</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45817</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45831</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45943</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>46034</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>46157</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55555,7 +55555,7 @@
         <v>46157</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>46160</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55701,7 +55701,7 @@
         <v>46157</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>46160</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>46161</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>46162</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56008,7 +56008,7 @@
         <v>46161</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>46161</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>46161</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>46161</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>46161</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>46161</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>46161</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46161</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45804</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46161</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>46161</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>46139</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>46167</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>46167</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>46167</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>45554</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>46170</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         <v>46171</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>46170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>46170</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57543,7 +57543,7 @@
         <v>46175</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>46175</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>46174</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>46184</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>46189</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>46189</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>46189</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45575</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>46191</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>46191</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>46191</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>46190</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>46191</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45575</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>46191</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58766,7 +58766,7 @@
         <v>46191</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>46191</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45952</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>46198</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46203</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46203</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>46203</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59385,7 +59385,7 @@
         <v>46206</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>46206</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59541,7 +59541,7 @@
         <v>46206</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>46213</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59697,7 +59697,7 @@
         <v>46213</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59770,7 +59770,7 @@
         <v>46213</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>46213</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59921,7 +59921,7 @@
         <v>46213</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59999,7 +59999,7 @@
         <v>46213</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>46213</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60150,7 +60150,7 @@
         <v>46219</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>46219</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>46219</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>46219</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46219</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>46219</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46220</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60681,7 +60681,7 @@
         <v>46220</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>46265</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>46265</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60915,7 +60915,7 @@
         <v>46038</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60988,7 +60988,7 @@
         <v>46038</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>46265</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>46265</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>46220</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61295,7 +61295,7 @@
         <v>46220</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61373,7 +61373,7 @@
         <v>46220</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61451,7 +61451,7 @@
         <v>46191</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61529,7 +61529,7 @@
         <v>46230</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61602,7 +61602,7 @@
         <v>46272</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>46268</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>46272</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>46276</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61899,7 +61899,7 @@
         <v>46279</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>45082</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>46191</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>46191</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>46285</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62284,7 +62284,7 @@
         <v>46285</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62362,7 +62362,7 @@
         <v>46286</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62440,7 +62440,7 @@
         <v>46285</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62518,7 +62518,7 @@
         <v>46283</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62591,7 +62591,7 @@
         <v>45974</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45954</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>46245</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62820,7 +62820,7 @@
         <v>46287</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>46287</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62966,7 +62966,7 @@
         <v>46287</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>46287</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>46290</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45726</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46293</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46252</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>46293</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>46293</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63575,7 +63575,7 @@
         <v>46293</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>46293</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63731,7 +63731,7 @@
         <v>46293</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63809,7 +63809,7 @@
         <v>46293</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>46248</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>46293</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         <v>46296</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64116,7 +64116,7 @@
         <v>46296</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         <v>46254</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64267,7 +64267,7 @@
         <v>46300</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64340,7 +64340,7 @@
         <v>46298</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64413,7 +64413,7 @@
         <v>46300</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64486,7 +64486,7 @@
         <v>46247</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>46300</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>46254</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>45645</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64788,7 +64788,7 @@
         <v>46296</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64861,7 +64861,7 @@
         <v>46253</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64939,7 +64939,7 @@
         <v>46302</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>46258</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65095,7 +65095,7 @@
         <v>46258</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>46260</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65251,7 +65251,7 @@
         <v>46303</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>46260</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65402,7 +65402,7 @@
         <v>46304</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65475,7 +65475,7 @@
         <v>46057</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65548,7 +65548,7 @@
         <v>44172</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65626,7 +65626,7 @@
         <v>44246</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65704,7 +65704,7 @@
         <v>44172</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65782,7 +65782,7 @@
         <v>45578</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65855,7 +65855,7 @@
         <v>45218</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65933,7 +65933,7 @@
         <v>45040</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66006,7 +66006,7 @@
         <v>45716</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66084,7 +66084,7 @@
         <v>45777</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         <v>45714</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>45832</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>45980</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>46094</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66469,7 +66469,7 @@
         <v>46111</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66542,7 +66542,7 @@
         <v>46128</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66620,7 +66620,7 @@
         <v>46245</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66698,7 +66698,7 @@
         <v>46296</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45138</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45905</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45967</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>46260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>46260</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45138</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45810</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>46283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>46289</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>46289</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46064</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>46148</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>46276</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>46191</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>46191</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45568</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45905</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45964</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>46191</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>46191</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44867</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>45905</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
         <v>45887</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>45099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45940</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46285</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>46260</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>44789</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>46038</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45952</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46141</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>46142</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>46191</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>46289</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>46289</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>46293</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45936</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>46293</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>46174</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>44484</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45980</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>46125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45068</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>46139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>46150</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46175</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>46239</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>46203</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>45905</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>45393</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>46064</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>46108</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>46191</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>46272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>46289</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>46289</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>46289</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>46174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>46245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44512</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44679</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44564</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45698</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45698</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>45698</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45411</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12417,7 +12417,7 @@
         <v>45645</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>45104</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45218</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>45922</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45007</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44949</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45946</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45946</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45946</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>45832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45953</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45537</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45138</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>45980</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>45980</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>44970</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45272</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45471</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>46112</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>46112</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>46125</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>46128</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>46128</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45281</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>44820</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>45376</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>44522</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>46150</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>46162</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46276</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>46191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>45250</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>46191</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>46293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>46293</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>46293</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45698</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45391</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>45698</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>44889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44853</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44495</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>44508</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44484</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>44503</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>44613</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44721</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>44722</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>44577</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>44862</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44481</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>44754</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>44638</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>44714</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44627</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>44790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44676</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44603</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>44630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>44862</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44671</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>44706</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>44671</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44577</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>44505</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>44546</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44823</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44522</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44635</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>44622</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44694</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>44484</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>44875</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44505</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44873</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>44491</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>44490</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>44536</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>44665</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>44629</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44777</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44608</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>44665</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>44539</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>44539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>44502</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20988,7 +20988,7 @@
         <v>44502</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>44594</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>44526</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>44481</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44487</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44889</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44784</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44650</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44497</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>44479</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44618</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44602</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44733</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44636</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44672</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44536</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>44825</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>44860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45355</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44511</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45412</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45189</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45264</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45091</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45393</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44490</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>44698</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45548</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>44784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>44928</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
         <v>45575</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>44927</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45618</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45471</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>45338</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23792,7 +23792,7 @@
         <v>45222</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23865,7 +23865,7 @@
         <v>45433</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45384</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>44865</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45303</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>45194</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45523</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45600</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45667</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45243</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45243</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24605,7 +24605,7 @@
         <v>45243</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44890</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45316</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24907,7 +24907,7 @@
         <v>45471</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>45103</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45751</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45108</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>45036</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45751</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45702</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45518</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>45061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45072</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44809</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25798,7 +25798,7 @@
         <v>44876</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>44902</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45103</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45611</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44866</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45043</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45107</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45694</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45604</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45884</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45525</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45532</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44902</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>45323</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44531</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45183</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45664</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44833</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>45884</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>45112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45568</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45341</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45334</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45274</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45152</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45887</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45518</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45134</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45575</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45273</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45162</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45279</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45519</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45537</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28554,7 +28554,7 @@
         <v>44883</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28627,7 +28627,7 @@
         <v>45889</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45107</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>45218</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45889</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>45462</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
         <v>45516</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45538</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29163,7 +29163,7 @@
         <v>45441</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45441</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45568</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>44984</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29470,7 +29470,7 @@
         <v>45111</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45005</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29616,7 +29616,7 @@
         <v>45005</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45488</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45471</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44978</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45586</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45714</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45103</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>45729</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45441</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45903</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44602</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30429,7 +30429,7 @@
         <v>45005</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45608</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>45439</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>44602</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45546</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30804,7 +30804,7 @@
         <v>45702</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45538</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>45538</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45384</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31101,7 +31101,7 @@
         <v>45400</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44551</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>44480</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>45289</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31398,7 +31398,7 @@
         <v>44981</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31471,7 +31471,7 @@
         <v>45702</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45148</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>45776</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31690,7 +31690,7 @@
         <v>44988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>45141</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31841,7 +31841,7 @@
         <v>45777</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45777</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32070,7 +32070,7 @@
         <v>45393</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45726</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>45571</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32299,7 +32299,7 @@
         <v>44544</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45518</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>45518</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45643</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45783</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>45509</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45645</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45567</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45460</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45280</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>45541</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45519</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45140</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45646</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>44908</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33487,7 +33487,7 @@
         <v>45569</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45518</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45749</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45203</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>45267</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>44574</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>45537</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>45229</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45170</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>44553</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>45537</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>45618</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>44594</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>45343</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>45400</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>45546</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>45219</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45925</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34919,7 +34919,7 @@
         <v>45330</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>45181</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45639</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45201</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>45177</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35299,7 +35299,7 @@
         <v>45565</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45418</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44888</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>45440</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>45562</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45667</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35742,7 +35742,7 @@
         <v>45565</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>45796</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35893,7 +35893,7 @@
         <v>45553</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35971,7 +35971,7 @@
         <v>44522</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36044,7 +36044,7 @@
         <v>44974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45795</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45796</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45796</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36346,7 +36346,7 @@
         <v>44621</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44949</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36492,7 +36492,7 @@
         <v>45054</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36565,7 +36565,7 @@
         <v>45218</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36643,7 +36643,7 @@
         <v>44943</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36716,7 +36716,7 @@
         <v>45244</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>45456</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45793</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36940,7 +36940,7 @@
         <v>44979</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>45590</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45201</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37164,7 +37164,7 @@
         <v>45201</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45155</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45456</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45229</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45194</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>44740</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45131</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45310</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45394</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>44683</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45582</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45769</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45667</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45610</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>45173</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45387</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45387</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45937</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38503,7 +38503,7 @@
         <v>45377</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>45548</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45168</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45569</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45372</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45813</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45937</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45095</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45095</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45628</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45251</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44963</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45940</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45940</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45940</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>45188</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44735</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45266</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>44967</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>44970</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>44577</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45348</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>44675</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>45125</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40290,7 +40290,7 @@
         <v>45099</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>45061</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>44822</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45821</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>45097</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45947</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45173</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45635</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>45952</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45177</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45685</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41113,7 +41113,7 @@
         <v>45628</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45827</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>45344</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45523</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45523</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45832</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41561,7 +41561,7 @@
         <v>45832</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45832</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45832</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45034</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45194</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45964</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45009</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>44503</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>45835</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>45145</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45159</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45158</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45516</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45488</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45194</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45538</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45511</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>45968</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45511</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44951</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45233</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45520</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45749</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45749</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45305</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45845</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45845</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45229</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>45756</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45974</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45974</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45694</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>44728</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45670</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>44665</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45149</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45646</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45170</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>45072</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45227</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45357</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>44546</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45113</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>45254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45768</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45440</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>44990</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>44753</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45213,7 +45213,7 @@
         <v>45575</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>45369</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45534</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45530</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45980</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45030</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45980</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45310</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45477</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>45874</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45274</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45194</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45979</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>45980</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46348,7 +46348,7 @@
         <v>45980</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46426,7 +46426,7 @@
         <v>45729</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44803</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45876</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>44900</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45265</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45880</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>44511</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46937,7 +46937,7 @@
         <v>45272</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45079</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45079</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47166,7 +47166,7 @@
         <v>45766</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45736</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45211</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45684</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47458,7 +47458,7 @@
         <v>46098</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44566</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>46101</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47682,7 +47682,7 @@
         <v>44990</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47755,7 +47755,7 @@
         <v>45257</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45097</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45251</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47974,7 +47974,7 @@
         <v>45736</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45077</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45075</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>46108</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>46108</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>44546</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45229</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>46108</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>46113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>44946</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45048</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45047</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48865,7 +48865,7 @@
         <v>45471</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>46115</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>46115</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>46114</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>46114</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>46115</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>46115</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>46115</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>46115</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>46115</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45547</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>46115</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>46121</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45995</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45995</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>46125</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45008</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>46126</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>46128</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>46128</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>46002</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>44895</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>46133</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50637,7 +50637,7 @@
         <v>44916</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>44979</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45575</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>45166</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50939,7 +50939,7 @@
         <v>45982</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51012,7 +51012,7 @@
         <v>45832</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45982</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>45404</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>44902</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51314,7 +51314,7 @@
         <v>45538</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51392,7 +51392,7 @@
         <v>46009</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45107</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46013</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>45189</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51684,7 +51684,7 @@
         <v>45478</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45791</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>44853</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51908,7 +51908,7 @@
         <v>45497</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45915</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>44906</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52127,7 +52127,7 @@
         <v>45139</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52205,7 +52205,7 @@
         <v>45237</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52278,7 +52278,7 @@
         <v>46030</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45932</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52424,7 +52424,7 @@
         <v>45252</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52497,7 +52497,7 @@
         <v>45474</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52575,7 +52575,7 @@
         <v>45610</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52648,7 +52648,7 @@
         <v>44577</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>45952</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52799,7 +52799,7 @@
         <v>45618</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45642</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52950,7 +52950,7 @@
         <v>45614</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>46035</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>46037</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53169,7 +53169,7 @@
         <v>46038</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45211</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>45559</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>44721</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53471,7 +53471,7 @@
         <v>45119</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45453</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53627,7 +53627,7 @@
         <v>44734</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>46044</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53773,7 +53773,7 @@
         <v>45832</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>44946</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>44958</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>44978</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54070,7 +54070,7 @@
         <v>44846</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54143,7 +54143,7 @@
         <v>45590</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54216,7 +54216,7 @@
         <v>45254</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54294,7 +54294,7 @@
         <v>45762</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>46049</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54440,7 +54440,7 @@
         <v>45074</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54513,7 +54513,7 @@
         <v>44868</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54591,7 +54591,7 @@
         <v>45093</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>46142</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>46056</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>46058</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>44791</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45106</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>46071</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45877</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45817</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45831</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45943</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>46034</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>46157</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55555,7 +55555,7 @@
         <v>46157</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55628,7 +55628,7 @@
         <v>46160</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55701,7 +55701,7 @@
         <v>46157</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55779,7 +55779,7 @@
         <v>46160</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>46161</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>46162</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56008,7 +56008,7 @@
         <v>46161</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>46161</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>46161</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56242,7 +56242,7 @@
         <v>46161</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>46161</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>46161</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56476,7 +56476,7 @@
         <v>46161</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46161</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56632,7 +56632,7 @@
         <v>45804</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46161</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>46161</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>46139</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>46167</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57012,7 +57012,7 @@
         <v>46167</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>46167</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57168,7 +57168,7 @@
         <v>45554</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>46170</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57324,7 +57324,7 @@
         <v>46171</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>46170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57470,7 +57470,7 @@
         <v>46170</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57543,7 +57543,7 @@
         <v>46175</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>46175</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57699,7 +57699,7 @@
         <v>46174</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57777,7 +57777,7 @@
         <v>46184</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57850,7 +57850,7 @@
         <v>46189</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>46189</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -57996,7 +57996,7 @@
         <v>46189</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58069,7 +58069,7 @@
         <v>45575</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58147,7 +58147,7 @@
         <v>46191</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58225,7 +58225,7 @@
         <v>46191</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58303,7 +58303,7 @@
         <v>46191</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58381,7 +58381,7 @@
         <v>46191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58459,7 +58459,7 @@
         <v>46190</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>46191</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45575</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58688,7 +58688,7 @@
         <v>46191</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58766,7 +58766,7 @@
         <v>46191</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>46191</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45952</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>46198</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>46198</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59151,7 +59151,7 @@
         <v>46203</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46203</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>46203</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59385,7 +59385,7 @@
         <v>46206</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>46206</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59541,7 +59541,7 @@
         <v>46206</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59619,7 +59619,7 @@
         <v>46213</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59697,7 +59697,7 @@
         <v>46213</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59770,7 +59770,7 @@
         <v>46213</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>46213</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59921,7 +59921,7 @@
         <v>46213</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59999,7 +59999,7 @@
         <v>46213</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>46213</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60150,7 +60150,7 @@
         <v>46219</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>46219</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>46219</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>46219</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46219</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>46219</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46220</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60681,7 +60681,7 @@
         <v>46220</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60759,7 +60759,7 @@
         <v>46265</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>46265</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60915,7 +60915,7 @@
         <v>46038</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60988,7 +60988,7 @@
         <v>46038</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>46265</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>46265</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61217,7 +61217,7 @@
         <v>46220</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61295,7 +61295,7 @@
         <v>46220</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61373,7 +61373,7 @@
         <v>46220</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61451,7 +61451,7 @@
         <v>46191</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61529,7 +61529,7 @@
         <v>46230</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61602,7 +61602,7 @@
         <v>46272</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61680,7 +61680,7 @@
         <v>46268</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>46272</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61826,7 +61826,7 @@
         <v>46276</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61899,7 +61899,7 @@
         <v>46279</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>45082</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>46191</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62128,7 +62128,7 @@
         <v>46191</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>46285</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62284,7 +62284,7 @@
         <v>46285</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62362,7 +62362,7 @@
         <v>46286</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62440,7 +62440,7 @@
         <v>46285</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62518,7 +62518,7 @@
         <v>46283</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62591,7 +62591,7 @@
         <v>45974</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45954</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62742,7 +62742,7 @@
         <v>46245</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62820,7 +62820,7 @@
         <v>46287</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>46287</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62966,7 +62966,7 @@
         <v>46287</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>46287</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>46290</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>45726</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46293</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63346,7 +63346,7 @@
         <v>46252</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63419,7 +63419,7 @@
         <v>46293</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63497,7 +63497,7 @@
         <v>46293</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63575,7 +63575,7 @@
         <v>46293</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63653,7 +63653,7 @@
         <v>46293</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63731,7 +63731,7 @@
         <v>46293</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63809,7 +63809,7 @@
         <v>46293</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63887,7 +63887,7 @@
         <v>46248</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>46293</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64038,7 +64038,7 @@
         <v>46296</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64116,7 +64116,7 @@
         <v>46296</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         <v>46254</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64267,7 +64267,7 @@
         <v>46300</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64340,7 +64340,7 @@
         <v>46298</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64413,7 +64413,7 @@
         <v>46300</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64486,7 +64486,7 @@
         <v>46247</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64564,7 +64564,7 @@
         <v>46300</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64637,7 +64637,7 @@
         <v>46254</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64710,7 +64710,7 @@
         <v>45645</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64788,7 +64788,7 @@
         <v>46296</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64861,7 +64861,7 @@
         <v>46253</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64939,7 +64939,7 @@
         <v>46302</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>46258</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65095,7 +65095,7 @@
         <v>46258</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65173,7 +65173,7 @@
         <v>46260</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65251,7 +65251,7 @@
         <v>46303</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>46260</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65402,7 +65402,7 @@
         <v>46304</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65475,7 +65475,7 @@
         <v>46057</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65548,7 +65548,7 @@
         <v>44172</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65626,7 +65626,7 @@
         <v>44246</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65704,7 +65704,7 @@
         <v>44172</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65782,7 +65782,7 @@
         <v>45578</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65855,7 +65855,7 @@
         <v>45218</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65933,7 +65933,7 @@
         <v>45040</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -66006,7 +66006,7 @@
         <v>45716</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66084,7 +66084,7 @@
         <v>45777</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66162,7 +66162,7 @@
         <v>45714</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>45832</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>45980</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66391,7 +66391,7 @@
         <v>46094</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66469,7 +66469,7 @@
         <v>46111</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66542,7 +66542,7 @@
         <v>46128</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66620,7 +66620,7 @@
         <v>46245</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66698,7 +66698,7 @@
         <v>46296</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45138</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45967</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46132</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>46203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45138</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>45810</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46283</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46289</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46283</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>46289</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>46064</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46276</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>46191</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>46191</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>46148</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45964</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45568</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45021</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46191</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>46191</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44867</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45905</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>45099</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45940</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46285</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>46141</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45085</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44789</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>46038</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45952</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>46191</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>46289</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46289</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>46293</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>46293</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45936</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>46174</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>46142</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45068</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45980</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>46125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>46175</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>46150</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>46239</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>46203</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>46260</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>45218</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>46048</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45393</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>46191</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>46064</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>46108</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>46272</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>46191</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>46289</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>46289</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>46289</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>46174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>46245</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>44512</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44693</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>44691</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>44679</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45376</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44949</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45281</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45138</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45559</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46146</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44522</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45922</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>46150</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45943</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45946</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45946</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>45946</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45946</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45953</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>46157</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44970</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>46162</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>45980</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45980</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45980</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45007</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45411</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>46112</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>46112</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>46125</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46128</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>46128</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44536</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45218</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>45104</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>46191</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45250</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>45471</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45698</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45698</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>46293</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>46293</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>46293</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44564</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45832</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45537</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45698</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45391</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45698</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44889</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44853</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44495</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44508</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>44503</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>44613</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>44721</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>44722</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>44862</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44577</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>44638</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>44754</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>44714</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>44627</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>44790</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44676</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>44630</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>44862</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>44603</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>44713</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>44671</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44706</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44577</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>44505</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44671</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44546</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44823</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>44522</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>44635</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44694</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44505</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>44490</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44629</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>44665</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>44594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>44487</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>44497</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44819</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>44733</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44672</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>44825</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>44622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>44875</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44491</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44526</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44889</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44602</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>44777</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44665</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44502</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>44502</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44491</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44784</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44536</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>44860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>44873</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44536</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>44608</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>44539</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44539</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>44650</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>44636</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>44618</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>44511</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44490</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44698</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>45310</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45736</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45530</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45289</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>44531</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45518</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>44967</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45439</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45107</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45532</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45112</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44974</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>44683</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45030</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45604</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45384</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>44943</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45646</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45158</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45054</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45140</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45751</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45611</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45183</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45194</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44853</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45568</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45074</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45575</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45305</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45488</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45097</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45610</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45243</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45243</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>45608</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45344</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45330</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45177</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45749</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>45541</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45243</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>45749</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>45272</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45075</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44988</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45497</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45369</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>44803</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>44888</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45162</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44928</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>44902</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45433</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>45108</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45173</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45310</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>44979</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>45168</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>45441</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45441</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45645</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45547</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>44551</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44574</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45610</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>44675</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>44865</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>44546</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>45103</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45194</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>44908</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
         <v>45471</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45471</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>45189</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>44900</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45148</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27998,7 +27998,7 @@
         <v>45152</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44577</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44503</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28373,7 +28373,7 @@
         <v>44951</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45131</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>45218</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45266</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45227</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45188</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45170</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>45384</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>45091</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>45201</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45538</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>45257</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45119</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45348</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45729</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45201</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>45201</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45518</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45932</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45139</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45538</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45832</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45488</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45614</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45316</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45393</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45222</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45884</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>44949</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>44895</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45887</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>45952</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>45323</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45889</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45889</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>44990</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>45642</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45769</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45072</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45884</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45477</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31597,7 +31597,7 @@
         <v>45832</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>44577</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>45093</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45106</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>45077</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31972,7 +31972,7 @@
         <v>44791</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>45915</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>45903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32196,7 +32196,7 @@
         <v>44846</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44594</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45252</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32415,7 +32415,7 @@
         <v>45177</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45265</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32566,7 +32566,7 @@
         <v>44522</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45343</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>45684</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45925</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>45134</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45237</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>44978</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>44868</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>44990</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45877</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44946</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33384,7 +33384,7 @@
         <v>45937</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45400</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>45173</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33613,7 +33613,7 @@
         <v>45813</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33686,7 +33686,7 @@
         <v>45937</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>44902</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33842,7 +33842,7 @@
         <v>45940</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45940</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33998,7 +33998,7 @@
         <v>45940</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45685</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34227,7 +34227,7 @@
         <v>45586</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45947</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45097</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>45548</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45831</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34602,7 +34602,7 @@
         <v>45440</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>45952</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34748,7 +34748,7 @@
         <v>45943</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45817</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34894,7 +34894,7 @@
         <v>46034</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45646</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45341</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45565</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35191,7 +35191,7 @@
         <v>46157</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45714</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>46157</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35415,7 +35415,7 @@
         <v>46157</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>46160</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35566,7 +35566,7 @@
         <v>46161</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>46161</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         <v>46161</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45229</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45964</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>46161</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36024,7 +36024,7 @@
         <v>46161</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>46160</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36175,7 +36175,7 @@
         <v>45538</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>46161</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45804</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36404,7 +36404,7 @@
         <v>44511</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36477,7 +36477,7 @@
         <v>46161</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36555,7 +36555,7 @@
         <v>46161</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46161</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36711,7 +36711,7 @@
         <v>45968</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>46161</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36867,7 +36867,7 @@
         <v>46161</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>45229</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37023,7 +37023,7 @@
         <v>46162</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>44602</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45974</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45974</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45980</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>45980</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45980</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>45979</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45980</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45229</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45565</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>46167</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45303</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45471</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>44734</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>44906</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>46167</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45047</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>45568</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>44984</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46167</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45273</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38684,7 +38684,7 @@
         <v>45394</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>46139</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45618</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45554</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45995</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45995</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>45355</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39205,7 +39205,7 @@
         <v>45702</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>46170</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>44979</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>46170</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39502,7 +39502,7 @@
         <v>46170</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>46002</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39648,7 +39648,7 @@
         <v>46171</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>44958</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45982</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45982</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45043</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45694</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>46009</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40164,7 +40164,7 @@
         <v>45751</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>45233</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40315,7 +40315,7 @@
         <v>46013</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>46174</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>44981</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45538</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45005</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45005</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45628</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45404</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44546</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45768</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45194</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44721</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44876</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45057</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41362,7 +41362,7 @@
         <v>45145</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46175</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45166</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>46030</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45338</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41742,7 +41742,7 @@
         <v>46175</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>46035</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45726</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>46037</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46038</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>45159</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45103</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45061</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45279</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>45523</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>44833</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46044</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>44927</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45274</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45149</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>46049</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>45523</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45766</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45600</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45036</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>46056</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         <v>45478</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>45518</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45518</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>45518</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>46058</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45548</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>46184</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>46189</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43884,7 +43884,7 @@
         <v>46189</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>46189</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>46071</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>45125</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>44841</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45061</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45170</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45562</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44546,7 +44546,7 @@
         <v>45474</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44624,7 +44624,7 @@
         <v>45511</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44697,7 +44697,7 @@
         <v>44978</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>44963</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44843,7 +44843,7 @@
         <v>45575</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45005</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>45575</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>46191</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>46191</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45952</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>46191</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45034</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45530,7 +45530,7 @@
         <v>46191</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>46191</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>46191</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>46191</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>46191</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45582</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>46098</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45635</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>46101</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>44740</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45194</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>46108</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>46198</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46519,7 +46519,7 @@
         <v>46108</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46592,7 +46592,7 @@
         <v>46108</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46665,7 +46665,7 @@
         <v>45628</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>46198</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>46114</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>46113</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -46962,7 +46962,7 @@
         <v>45756</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         <v>46114</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>46115</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>46115</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>46115</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46115</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>46115</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47473,7 +47473,7 @@
         <v>46115</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47546,7 +47546,7 @@
         <v>46115</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>46115</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45702</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>46121</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45218</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46126</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>46125</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45590</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48135,7 +48135,7 @@
         <v>46128</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48213,7 +48213,7 @@
         <v>46128</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>46128</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>46203</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>46133</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48520,7 +48520,7 @@
         <v>46203</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45072</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         <v>46203</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45537</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -48827,7 +48827,7 @@
         <v>45519</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45412</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45387</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45387</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45141</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45400</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>45791</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>46206</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>44970</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45194</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>44866</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45538</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>46206</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>44621</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45009</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50020,7 +50020,7 @@
         <v>44566</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>46213</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46213</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46213</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>46213</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>45667</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45667</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>46213</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>46213</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>46213</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>45575</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>44602</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>46220</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -50999,7 +50999,7 @@
         <v>46220</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>46219</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>45103</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>46220</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>46220</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>46219</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46219</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>46038</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46220</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>46038</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>45511</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>44735</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>46219</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>46219</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>46219</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>45111</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>44883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45254</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>45525</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46230</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>46272</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45177</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>45251</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -52728,7 +52728,7 @@
         <v>46272</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45393</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45762</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>46191</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45107</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>44902</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53181,7 +53181,7 @@
         <v>45519</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45107</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44822</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45274</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>46276</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53556,7 +53556,7 @@
         <v>45254</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>45736</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>46279</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>45095</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -53853,7 +53853,7 @@
         <v>45571</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>46191</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>46191</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>44916</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54160,7 +54160,7 @@
         <v>45170</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>45546</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54316,7 +54316,7 @@
         <v>45082</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54394,7 +54394,7 @@
         <v>45211</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54472,7 +54472,7 @@
         <v>44544</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>46283</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54618,7 +54618,7 @@
         <v>45471</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54691,7 +54691,7 @@
         <v>45974</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -54764,7 +54764,7 @@
         <v>45954</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -54842,7 +54842,7 @@
         <v>46286</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -54920,7 +54920,7 @@
         <v>45189</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45372</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>46287</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45079</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>45079</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45462</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55368,7 +55368,7 @@
         <v>46285</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55446,7 +55446,7 @@
         <v>46287</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45575</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>46285</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55680,7 +55680,7 @@
         <v>45441</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55753,7 +55753,7 @@
         <v>46285</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>45553</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -55909,7 +55909,7 @@
         <v>45729</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -55982,7 +55982,7 @@
         <v>45008</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>46245</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>45095</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45377</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>46287</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>45664</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>46293</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45274</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56727,7 +56727,7 @@
         <v>45280</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45726</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>46293</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -56956,7 +56956,7 @@
         <v>46293</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57034,7 +57034,7 @@
         <v>46290</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57112,7 +57112,7 @@
         <v>46293</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57190,7 +57190,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>44890</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>46248</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>45334</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57487,7 +57487,7 @@
         <v>46293</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>46293</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57643,7 +57643,7 @@
         <v>45516</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>44753</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57789,7 +57789,7 @@
         <v>46293</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45251</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45643</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45569</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>45618</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>45119</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58242,7 +58242,7 @@
         <v>46252</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         <v>44946</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58388,7 +58388,7 @@
         <v>44809</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58461,7 +58461,7 @@
         <v>45264</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>46247</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>46254</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>46296</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58763,7 +58763,7 @@
         <v>46254</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>46253</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>46296</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -58992,7 +58992,7 @@
         <v>46296</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59065,7 +59065,7 @@
         <v>45645</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59143,7 +59143,7 @@
         <v>45702</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59216,7 +59216,7 @@
         <v>45219</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>44665</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>45211</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>46258</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59518,7 +59518,7 @@
         <v>45453</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59596,7 +59596,7 @@
         <v>45777</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59674,7 +59674,7 @@
         <v>45777</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>45776</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>46300</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -59898,7 +59898,7 @@
         <v>45783</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>46258</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>45567</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45509</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>45460</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>46298</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45569</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>45253</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45203</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>46300</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45229</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45267</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>46300</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>45537</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45537</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61023,7 +61023,7 @@
         <v>45639</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61096,7 +61096,7 @@
         <v>45181</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61174,7 +61174,7 @@
         <v>45418</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61247,7 +61247,7 @@
         <v>45618</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>46303</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45667</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61476,7 +61476,7 @@
         <v>45546</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61549,7 +61549,7 @@
         <v>45440</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61622,7 +61622,7 @@
         <v>46302</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61700,7 +61700,7 @@
         <v>46260</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61778,7 +61778,7 @@
         <v>46307</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61856,7 +61856,7 @@
         <v>45793</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -61934,7 +61934,7 @@
         <v>45456</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62012,7 +62012,7 @@
         <v>45795</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62085,7 +62085,7 @@
         <v>45155</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>45244</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>46304</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>45796</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>45796</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62460,7 +62460,7 @@
         <v>45796</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62538,7 +62538,7 @@
         <v>45456</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62611,7 +62611,7 @@
         <v>46057</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62684,7 +62684,7 @@
         <v>46307</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62762,7 +62762,7 @@
         <v>45590</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>46265</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -62913,7 +62913,7 @@
         <v>46308</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -62986,7 +62986,7 @@
         <v>46308</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63059,7 +63059,7 @@
         <v>46308</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63132,7 +63132,7 @@
         <v>46308</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63205,7 +63205,7 @@
         <v>46265</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63283,7 +63283,7 @@
         <v>46308</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63356,7 +63356,7 @@
         <v>46265</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63434,7 +63434,7 @@
         <v>46308</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63507,7 +63507,7 @@
         <v>46308</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63580,7 +63580,7 @@
         <v>46265</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63658,7 +63658,7 @@
         <v>46311</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63731,7 +63731,7 @@
         <v>45821</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63809,7 +63809,7 @@
         <v>46268</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63882,7 +63882,7 @@
         <v>45827</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -63960,7 +63960,7 @@
         <v>45523</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64033,7 +64033,7 @@
         <v>45832</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64111,7 +64111,7 @@
         <v>45832</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64189,7 +64189,7 @@
         <v>45832</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64267,7 +64267,7 @@
         <v>45832</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>45835</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45516</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64496,7 +64496,7 @@
         <v>45845</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>45520</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45845</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>44728</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64793,7 +64793,7 @@
         <v>45694</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64866,7 +64866,7 @@
         <v>45670</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -64939,7 +64939,7 @@
         <v>45534</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>45831</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65090,7 +65090,7 @@
         <v>45575</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65168,7 +65168,7 @@
         <v>45874</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65246,7 +65246,7 @@
         <v>45876</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65319,7 +65319,7 @@
         <v>45880</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65392,7 +65392,7 @@
         <v>44172</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65470,7 +65470,7 @@
         <v>44172</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65548,7 +65548,7 @@
         <v>44246</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65626,7 +65626,7 @@
         <v>45578</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65699,7 +65699,7 @@
         <v>45218</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65777,7 +65777,7 @@
         <v>45040</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65850,7 +65850,7 @@
         <v>45716</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65928,7 +65928,7 @@
         <v>45777</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66006,7 +66006,7 @@
         <v>45714</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66079,7 +66079,7 @@
         <v>45832</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66157,7 +66157,7 @@
         <v>45980</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66235,7 +66235,7 @@
         <v>46094</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66313,7 +66313,7 @@
         <v>46111</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66386,7 +66386,7 @@
         <v>46128</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66464,7 +66464,7 @@
         <v>46245</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66542,7 +66542,7 @@
         <v>46296</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45138</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45967</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46132</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45810</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45138</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>46283</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46289</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46289</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>46276</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46283</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>46289</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>46064</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46148</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>46191</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>46191</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46276</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>46191</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46191</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45568</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44867</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45905</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>45940</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46285</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45085</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46289</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>46293</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>46293</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>46038</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45952</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>46142</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>46141</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>46174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45068</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>46175</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46125</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>46139</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>46191</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46289</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>46289</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>46289</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>46064</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>46108</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>46272</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>46174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46245</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45393</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44691</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44679</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45281</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>46162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45698</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45698</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45698</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45376</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45946</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45946</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45946</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45946</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45953</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45411</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45980</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>46191</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45250</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46293</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>46293</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45832</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45537</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>46112</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>46112</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>46125</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>46128</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46128</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45218</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44820</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45007</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45559</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>46150</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45138</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44564</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45104</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44536</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44970</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45272</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45471</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45698</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45391</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44853</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44495</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44508</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44503</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44613</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44722</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44862</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44577</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44754</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44714</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>44627</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44790</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>44676</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44603</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44630</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44862</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44671</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44706</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44577</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44505</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44671</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44546</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44823</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44522</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44635</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44694</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44505</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>44629</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>44665</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44497</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44819</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44733</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44672</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>44622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>44875</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>44889</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44777</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>44665</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44502</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44784</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44536</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44860</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44873</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44536</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44608</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44539</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44539</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44650</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>44636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>44618</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44511</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45575</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44698</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45166</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45338</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45194</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45889</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45404</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44902</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45189</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45478</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45355</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45412</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45884</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44853</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45497</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46157</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>46160</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44906</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46161</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>46161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>46161</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>46161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>46161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>46161</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46161</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>46161</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>46161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45237</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45804</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>46161</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45091</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46161</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45474</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45610</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44577</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45618</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46139</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>46167</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>46167</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45211</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>44721</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45554</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45119</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45453</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44734</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44946</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>44958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>46170</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44978</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>46171</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>46170</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>46170</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>46175</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>44846</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46175</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45590</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45254</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45762</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45074</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45813</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44868</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>46174</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45940</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45940</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45189</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45940</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45222</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45433</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45384</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45243</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45243</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44890</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45471</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45518</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45575</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45061</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44809</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>44876</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45471</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44866</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45057</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45947</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>44865</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45952</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45303</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45523</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45667</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45170</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45103</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45036</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>46184</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45072</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45964</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>46189</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44902</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>46189</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46189</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45575</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45611</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46191</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46191</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45043</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46191</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>46190</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46191</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46191</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46191</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45604</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45952</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45525</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45532</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45974</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45974</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46198</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45664</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>44833</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45568</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45341</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45334</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>46203</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45979</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45980</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>45980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>46203</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45273</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46203</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45218</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45462</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>44902</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45516</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45568</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44984</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45111</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46206</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45471</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45714</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45103</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45729</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46213</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>46213</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>46213</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46213</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>46213</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>46213</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>46213</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45323</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45439</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45702</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45538</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45384</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45400</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>46219</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>46219</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>46219</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46219</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>46219</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46219</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45702</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46220</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46220</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45776</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46038</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>46038</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>46220</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>46220</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>46220</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45777</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46002</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45777</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46191</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>46230</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45783</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45509</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45567</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45460</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45982</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45982</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>46279</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>46009</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45569</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45253</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>46013</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45267</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45537</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45229</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45537</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45618</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45546</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45082</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>46191</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>46191</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>46030</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46285</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>46285</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>46286</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>45181</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45112</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45639</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>46285</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45418</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45667</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45796</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45795</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46283</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45274</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45796</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45796</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45974</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>46037</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46038</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45954</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>45152</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46245</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45244</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45456</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45793</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>46287</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>46044</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>46287</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45590</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45155</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45456</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>46287</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>46049</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45518</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>46056</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>46058</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46290</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45726</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46293</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>46252</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46293</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46293</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46293</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>46293</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>46293</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>46293</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>46248</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>46293</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>46071</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>44883</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>45821</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>46296</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46296</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45827</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45523</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45832</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45832</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45832</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45832</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>46254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>46300</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>46298</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>46300</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45835</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>46247</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>45516</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46300</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>46254</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45645</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45538</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>46296</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45441</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45441</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>46098</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45520</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45845</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>46253</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45845</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>46101</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>46302</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45005</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45005</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45694</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44728</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45488</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45670</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>44978</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45586</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46108</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>46108</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>46258</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>46108</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>46113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>46115</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>46115</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>46114</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>46114</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>46115</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>46115</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>46115</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>46115</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46115</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>46115</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45575</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45831</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45441</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45534</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>46260</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>46303</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>44602</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46121</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>44602</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45874</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46125</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46126</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46304</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45876</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46128</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46128</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>46128</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>46265</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45880</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>46308</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>46308</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>46308</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>46265</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45538</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>46133</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>46307</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>46308</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45884</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>46308</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>46308</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>46265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44988</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>46057</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45393</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45726</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45571</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>44544</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>44841</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>46308</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45832</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45645</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45280</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45541</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45519</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45538</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>44908</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45518</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45749</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45791</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>44574</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45915</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>44553</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45139</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>46268</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44594</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45932</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45252</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45400</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45952</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>46265</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45642</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>46311</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>45614</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>45201</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45565</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>46316</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>46316</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>44888</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>45832</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>46316</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45562</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>46272</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45565</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>46315</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45553</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>44974</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>44949</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>46272</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>46316</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>44943</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44979</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45387</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45093</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45201</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45201</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>46318</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>46318</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>44791</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45229</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52933,7 +52933,7 @@
         <v>45194</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45106</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>44740</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>45394</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45582</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>46276</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45095</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45769</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>46317</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45387</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53668,7 +53668,7 @@
         <v>45377</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>45548</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45569</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45877</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45095</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45251</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44963</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>44735</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45817</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45831</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45266</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>44967</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54559,7 +54559,7 @@
         <v>45943</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54632,7 +54632,7 @@
         <v>46034</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>44970</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45348</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>46157</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54929,7 +54929,7 @@
         <v>46157</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55002,7 +55002,7 @@
         <v>46160</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         <v>45099</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45635</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45628</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45344</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45034</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45194</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45009</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>44503</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45145</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45159</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45488</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45538</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45511</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>45511</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56112,7 +56112,7 @@
         <v>44951</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>44665</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45149</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>45646</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45170</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>45072</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>44546</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>45113</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>44990</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>45530</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>45030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45194</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>44900</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>44511</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45766</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45211</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>44566</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>44990</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45251</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45736</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45077</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>45075</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57748,7 +57748,7 @@
         <v>44946</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>45264</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>45393</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45548</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58050,7 +58050,7 @@
         <v>44928</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>44927</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45618</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>45600</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>45316</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>45177</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58498,7 +58498,7 @@
         <v>45751</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45108</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58644,7 +58644,7 @@
         <v>45751</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58717,7 +58717,7 @@
         <v>45702</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58790,7 +58790,7 @@
         <v>45103</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45119</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>45107</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45694</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59092,7 +59092,7 @@
         <v>44531</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>45575</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59243,7 +59243,7 @@
         <v>45162</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>45279</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>45519</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45537</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45107</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59618,7 +59618,7 @@
         <v>45005</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45608</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59769,7 +59769,7 @@
         <v>45546</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>44551</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45289</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>44981</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45148</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45141</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>45113</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45518</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>45518</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>45643</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45140</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>45646</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45170</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45343</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>45219</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45330</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45177</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>44522</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>44621</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61176,7 +61176,7 @@
         <v>45054</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61249,7 +61249,7 @@
         <v>45218</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45131</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>45310</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61473,7 +61473,7 @@
         <v>44683</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61546,7 +61546,7 @@
         <v>45667</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61619,7 +61619,7 @@
         <v>45610</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45173</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45168</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45372</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45628</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61984,7 +61984,7 @@
         <v>45188</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>44577</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>44675</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62208,7 +62208,7 @@
         <v>45125</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62281,7 +62281,7 @@
         <v>45061</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>44822</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45097</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62500,7 +62500,7 @@
         <v>45173</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62573,7 +62573,7 @@
         <v>45177</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         <v>45685</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45523</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>45265</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62870,7 +62870,7 @@
         <v>45158</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62943,7 +62943,7 @@
         <v>45194</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45233</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45749</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63167,7 +63167,7 @@
         <v>45749</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63240,7 +63240,7 @@
         <v>45305</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63313,7 +63313,7 @@
         <v>45229</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45756</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63459,7 +63459,7 @@
         <v>45227</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63532,7 +63532,7 @@
         <v>45357</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>45254</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45768</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63761,7 +63761,7 @@
         <v>45440</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
         <v>44753</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45369</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63980,7 +63980,7 @@
         <v>45310</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45477</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45274</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45729</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>44803</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>45265</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45272</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45079</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>45079</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45736</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45684</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64793,7 +64793,7 @@
         <v>45257</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64866,7 +64866,7 @@
         <v>45097</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64939,7 +64939,7 @@
         <v>44546</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65012,7 +65012,7 @@
         <v>45229</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65085,7 +65085,7 @@
         <v>45048</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65158,7 +65158,7 @@
         <v>45047</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65231,7 +65231,7 @@
         <v>45471</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45547</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65377,7 +65377,7 @@
         <v>45008</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>44895</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>44916</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>44979</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>44172</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>44246</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65830,7 +65830,7 @@
         <v>44172</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65908,7 +65908,7 @@
         <v>45578</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65981,7 +65981,7 @@
         <v>45218</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66059,7 +66059,7 @@
         <v>45040</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66132,7 +66132,7 @@
         <v>45716</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45777</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66288,7 +66288,7 @@
         <v>45714</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66361,7 +66361,7 @@
         <v>45832</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66439,7 +66439,7 @@
         <v>45980</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66517,7 +66517,7 @@
         <v>46094</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66595,7 +66595,7 @@
         <v>46111</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>46128</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66746,7 +66746,7 @@
         <v>46245</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66824,7 +66824,7 @@
         <v>46296</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>

--- a/Översikt LINDESBERG.xlsx
+++ b/Översikt LINDESBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45615</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46009</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45334</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>46175</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>44615</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45905</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>46064</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45905</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45252</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>46260</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44850</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>45905</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>45138</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>46064</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>46064</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>45967</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>45905</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45905</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>46203</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46132</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45810</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45138</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>46283</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46289</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46289</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>46276</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>46283</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>46289</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>46064</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>46148</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>46191</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>46191</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46276</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>45905</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45964</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>46191</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46191</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>45568</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>45099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>44867</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45905</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>45887</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6720,7 +6720,7 @@
         <v>45940</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>45099</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>46285</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44789</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45085</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>46289</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>46293</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>46293</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>46038</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45952</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46191</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>46142</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>46141</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>46174</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45068</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45980</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>46175</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46239</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>46287</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>46203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>46125</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>46139</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>46260</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>45218</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>46048</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>45905</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>46191</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>46289</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>46289</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
         <v>46289</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>46064</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>46108</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>46191</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>46272</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>46174</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>46245</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         <v>45393</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44691</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44679</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45281</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>46162</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>45922</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45698</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45698</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45698</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45376</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>45937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44522</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45943</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>45946</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45946</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45946</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45946</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45953</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45411</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>45645</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45980</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45980</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>46191</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45250</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46293</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>46293</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>46293</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45832</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>45537</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>46112</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14945,7 +14945,7 @@
         <v>46112</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>46125</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>46128</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>46128</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45218</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44820</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45007</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45559</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>46150</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45138</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>44564</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>45104</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44536</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44970</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>45272</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45471</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45698</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45391</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45698</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44853</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44495</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44508</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44503</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>44613</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44721</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44722</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>44862</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44577</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>44754</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44638</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>44714</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>44627</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>44790</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>44676</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44603</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44630</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>44862</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>44713</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44671</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>44706</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>44577</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44505</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44671</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>44546</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>44823</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>44522</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44635</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19473,7 +19473,7 @@
         <v>44694</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44505</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19624,7 +19624,7 @@
         <v>44629</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19697,7 +19697,7 @@
         <v>44665</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19843,7 +19843,7 @@
         <v>44497</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>44819</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44733</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>44672</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>44825</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>44622</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>44875</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44526</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>44889</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44602</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44777</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>44665</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44502</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44502</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44784</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44536</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>44860</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>44873</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44536</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44608</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44539</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21396,7 +21396,7 @@
         <v>44539</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>44650</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21542,7 +21542,7 @@
         <v>44636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>44618</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44511</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45575</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45887</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44698</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44784</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45166</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45338</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>45194</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22370,7 +22370,7 @@
         <v>45889</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45404</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44902</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45107</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45274</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45189</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45478</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45355</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45412</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45884</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44853</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45497</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>46157</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>46160</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>44906</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>46161</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>46161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23797,7 +23797,7 @@
         <v>46161</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>46161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>46161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>46161</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>46161</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -24187,7 +24187,7 @@
         <v>46161</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>46161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45237</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45804</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>46161</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45091</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46161</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45474</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45610</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>44577</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45618</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46139</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>46167</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>46167</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45211</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>44721</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45554</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45119</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45925</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45453</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44734</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>44946</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>44958</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>46170</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>44978</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -26160,7 +26160,7 @@
         <v>46171</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26233,7 +26233,7 @@
         <v>46170</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>46170</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>46175</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
         <v>44846</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>46175</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26608,7 +26608,7 @@
         <v>45590</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45254</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45762</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>45074</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>45813</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -27134,7 +27134,7 @@
         <v>44868</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>46174</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27290,7 +27290,7 @@
         <v>45940</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45940</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45189</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45940</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45222</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45433</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45384</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45243</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27967,7 +27967,7 @@
         <v>45243</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44890</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45471</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45518</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>45575</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45061</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44809</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>44876</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45471</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44866</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45057</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45947</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>44865</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45952</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45303</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45523</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45667</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>45170</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45103</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45036</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>46184</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45072</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45964</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>46189</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44902</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>46189</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46189</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45575</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45611</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46191</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46191</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45043</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>46191</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>46190</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46191</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45968</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>45575</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46191</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46191</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>46191</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45604</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45952</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45525</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45532</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45974</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45974</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>46198</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31576,7 +31576,7 @@
         <v>45183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45664</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>44833</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>45980</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>45568</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45341</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32180,7 +32180,7 @@
         <v>45334</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
         <v>46203</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45979</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45980</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>45980</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>46203</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>45273</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46203</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45218</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45462</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>44902</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45516</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45568</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44984</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45111</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>46206</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46206</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45471</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>46206</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>45714</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>45103</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45729</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46213</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>46213</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>46213</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34075,7 +34075,7 @@
         <v>46213</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>46213</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34226,7 +34226,7 @@
         <v>46213</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34304,7 +34304,7 @@
         <v>45099</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>46213</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34455,7 +34455,7 @@
         <v>45323</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45439</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45995</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45702</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>45538</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45384</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45400</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35049,7 +35049,7 @@
         <v>46219</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35122,7 +35122,7 @@
         <v>46219</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>46219</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46219</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>46219</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>46219</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45702</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46220</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46220</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45776</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46038</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>46038</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>46220</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>46220</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>46220</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45777</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46002</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45777</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>46191</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>46230</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45783</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>45509</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45567</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45460</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45982</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45982</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>46279</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>46009</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45569</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45253</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45203</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>46013</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>45267</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45537</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>45229</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37679,7 +37679,7 @@
         <v>45537</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37757,7 +37757,7 @@
         <v>45618</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45546</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37903,7 +37903,7 @@
         <v>45082</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>46191</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>46191</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>46030</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46285</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>46285</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>46286</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>45181</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45112</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45639</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>46285</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45418</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38892,7 +38892,7 @@
         <v>45667</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45796</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45795</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46283</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45274</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45796</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45796</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45974</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>46037</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46038</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45954</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>45152</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46245</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45244</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45456</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45793</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>46287</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>46044</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>46287</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45590</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45155</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>45456</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>46287</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>46049</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45518</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>45134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>46056</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>46058</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46290</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45726</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46293</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>46252</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46293</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46293</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>46293</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41590,7 +41590,7 @@
         <v>46293</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41668,7 +41668,7 @@
         <v>46293</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>46293</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>46248</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>46293</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>46071</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>44883</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>45821</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>46296</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46296</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45827</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45523</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>45832</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45832</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45832</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45832</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42813,7 +42813,7 @@
         <v>46254</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>46300</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>46298</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>46300</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45835</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>46247</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>45516</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46300</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>46254</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45645</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45538</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>46296</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45441</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45441</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>46098</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45520</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45845</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>46253</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44177,7 +44177,7 @@
         <v>45845</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>46101</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44323,7 +44323,7 @@
         <v>46302</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>45005</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>45005</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45694</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44728</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45488</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44771,7 +44771,7 @@
         <v>45670</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>46258</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>44978</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45586</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>46108</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45141,7 +45141,7 @@
         <v>46108</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45214,7 +45214,7 @@
         <v>46258</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>46108</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>46113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45443,7 +45443,7 @@
         <v>46115</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>46115</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>46114</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>46114</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>46115</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>46115</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45881,7 +45881,7 @@
         <v>46115</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45954,7 +45954,7 @@
         <v>46115</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46115</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46100,7 +46100,7 @@
         <v>46115</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45575</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45831</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45441</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45534</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>46260</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>46303</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46631,7 +46631,7 @@
         <v>44602</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46121</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>44602</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46850,7 +46850,7 @@
         <v>45874</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46928,7 +46928,7 @@
         <v>46125</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>46126</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46304</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45876</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>46128</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>46128</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>46128</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>46265</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45880</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>46308</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>46308</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>46308</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>46265</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>45538</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>46133</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>46307</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48126,7 +48126,7 @@
         <v>46308</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45884</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48272,7 +48272,7 @@
         <v>46308</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48345,7 +48345,7 @@
         <v>46308</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>46265</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44988</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>46057</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45393</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45726</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45571</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>44544</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>44841</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49022,7 +49022,7 @@
         <v>46308</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45832</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45645</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45280</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45541</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>45519</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45538</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49641,7 +49641,7 @@
         <v>44908</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49714,7 +49714,7 @@
         <v>45518</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49787,7 +49787,7 @@
         <v>45749</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49860,7 +49860,7 @@
         <v>45791</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>44574</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>45915</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>44553</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45139</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>46268</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>44594</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45932</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45252</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>45400</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45952</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>46265</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45642</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>46311</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>45614</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>45201</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45565</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>46316</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>46316</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>44888</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>45832</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>46316</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45562</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>46272</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45565</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51735,7 +51735,7 @@
         <v>46315</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51808,7 +51808,7 @@
         <v>45553</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>44974</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>44949</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>46272</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>46316</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>44943</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44979</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45387</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45093</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45201</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52553,7 +52553,7 @@
         <v>45201</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>46318</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>46318</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52782,7 +52782,7 @@
         <v>44791</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45229</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52933,7 +52933,7 @@
         <v>45194</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45106</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53079,7 +53079,7 @@
         <v>44740</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>45394</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>45582</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>46276</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>45095</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45769</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>46317</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53595,7 +53595,7 @@
         <v>45387</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53668,7 +53668,7 @@
         <v>45377</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53741,7 +53741,7 @@
         <v>45548</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53819,7 +53819,7 @@
         <v>45569</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53892,7 +53892,7 @@
         <v>45877</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45095</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54043,7 +54043,7 @@
         <v>45251</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>44963</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54189,7 +54189,7 @@
         <v>44735</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54267,7 +54267,7 @@
         <v>45817</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>45831</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54413,7 +54413,7 @@
         <v>45266</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>44967</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54559,7 +54559,7 @@
         <v>45943</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54632,7 +54632,7 @@
         <v>46034</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>44970</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45348</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>46157</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -54929,7 +54929,7 @@
         <v>46157</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55002,7 +55002,7 @@
         <v>46160</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         <v>45099</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45635</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45628</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45344</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45034</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45194</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45009</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>44503</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45145</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45159</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45488</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45538</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>45511</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>45511</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56112,7 +56112,7 @@
         <v>44951</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>44665</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45149</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>45646</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45170</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56487,7 +56487,7 @@
         <v>45072</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>44546</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>45113</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>44990</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>45530</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>45030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45194</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>44900</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>44511</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57154,7 +57154,7 @@
         <v>45766</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57227,7 +57227,7 @@
         <v>45211</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57300,7 +57300,7 @@
         <v>44566</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57373,7 +57373,7 @@
         <v>44990</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57446,7 +57446,7 @@
         <v>45251</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57519,7 +57519,7 @@
         <v>45736</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45077</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57670,7 +57670,7 @@
         <v>45075</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57748,7 +57748,7 @@
         <v>44946</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>45264</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>45393</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45548</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58050,7 +58050,7 @@
         <v>44928</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>44927</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45618</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58274,7 +58274,7 @@
         <v>45600</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>45316</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>45177</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58498,7 +58498,7 @@
         <v>45751</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58571,7 +58571,7 @@
         <v>45108</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58644,7 +58644,7 @@
         <v>45751</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58717,7 +58717,7 @@
         <v>45702</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -58790,7 +58790,7 @@
         <v>45103</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -58863,7 +58863,7 @@
         <v>45119</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -58941,7 +58941,7 @@
         <v>45107</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45694</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59092,7 +59092,7 @@
         <v>44531</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59165,7 +59165,7 @@
         <v>45575</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59243,7 +59243,7 @@
         <v>45162</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>45279</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59389,7 +59389,7 @@
         <v>45519</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>45537</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>45107</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59618,7 +59618,7 @@
         <v>45005</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45608</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -59769,7 +59769,7 @@
         <v>45546</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -59847,7 +59847,7 @@
         <v>44551</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -59920,7 +59920,7 @@
         <v>45289</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>44981</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45148</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45141</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>45113</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45518</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>45518</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>45643</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>45140</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>45646</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>45170</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45343</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>45219</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45330</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45177</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>44522</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>44621</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -61176,7 +61176,7 @@
         <v>45054</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -61249,7 +61249,7 @@
         <v>45218</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45131</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>45310</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -61473,7 +61473,7 @@
         <v>44683</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -61546,7 +61546,7 @@
         <v>45667</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -61619,7 +61619,7 @@
         <v>45610</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45173</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45168</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45372</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45628</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -61984,7 +61984,7 @@
         <v>45188</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>44577</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>44675</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -62208,7 +62208,7 @@
         <v>45125</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -62281,7 +62281,7 @@
         <v>45061</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>44822</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45097</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -62500,7 +62500,7 @@
         <v>45173</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -62573,7 +62573,7 @@
         <v>45177</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         <v>45685</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45523</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>45265</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -62870,7 +62870,7 @@
         <v>45158</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -62943,7 +62943,7 @@
         <v>45194</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45233</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45749</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -63167,7 +63167,7 @@
         <v>45749</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -63240,7 +63240,7 @@
         <v>45305</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -63313,7 +63313,7 @@
         <v>45229</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45756</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -63459,7 +63459,7 @@
         <v>45227</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -63532,7 +63532,7 @@
         <v>45357</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -63610,7 +63610,7 @@
         <v>45254</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>45768</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -63761,7 +63761,7 @@
         <v>45440</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -63834,7 +63834,7 @@
         <v>44753</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -63907,7 +63907,7 @@
         <v>45369</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -63980,7 +63980,7 @@
         <v>45310</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -64053,7 +64053,7 @@
         <v>45477</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -64126,7 +64126,7 @@
         <v>45274</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45729</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -64272,7 +64272,7 @@
         <v>44803</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>45265</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -64418,7 +64418,7 @@
         <v>45272</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -64491,7 +64491,7 @@
         <v>45079</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>45079</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -64647,7 +64647,7 @@
         <v>45736</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -64720,7 +64720,7 @@
         <v>45684</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -64793,7 +64793,7 @@
         <v>45257</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -64866,7 +64866,7 @@
         <v>45097</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -64939,7 +64939,7 @@
         <v>44546</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -65012,7 +65012,7 @@
         <v>45229</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -65085,7 +65085,7 @@
         <v>45048</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -65158,7 +65158,7 @@
         <v>45047</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -65231,7 +65231,7 @@
         <v>45471</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>45547</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -65377,7 +65377,7 @@
         <v>45008</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>44895</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>44916</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -65601,7 +65601,7 @@
         <v>44979</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -65674,7 +65674,7 @@
         <v>44172</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>44246</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -65830,7 +65830,7 @@
         <v>44172</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -65908,7 +65908,7 @@
         <v>45578</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -65981,7 +65981,7 @@
         <v>45218</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -66059,7 +66059,7 @@
         <v>45040</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -66132,7 +66132,7 @@
         <v>45716</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -66210,7 +66210,7 @@
         <v>45777</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -66288,7 +66288,7 @@
         <v>45714</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -66361,7 +66361,7 @@
         <v>45832</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -66439,7 +66439,7 @@
         <v>45980</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -66517,7 +66517,7 @@
         <v>46094</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -66595,7 +66595,7 @@
         <v>46111</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>46128</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -66746,7 +66746,7 @@
         <v>46245</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -66824,7 +66824,7 @@
         <v>46296</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
